--- a/research/traditional_assets/database/data/israel/israel_power.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_power.xlsx
@@ -1400,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1537,22 +1537,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07459822422242116</v>
+        <v>0.0744612983067096</v>
       </c>
       <c r="C2">
-        <v>3809.916681848994</v>
+        <v>3790.602025052492</v>
       </c>
       <c r="D2">
-        <v>3500.316681848994</v>
+        <v>3517.039025052492</v>
       </c>
       <c r="E2">
-        <v>-1520.7</v>
+        <v>-1484.663</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>36.037</v>
       </c>
       <c r="G2">
         <v>309.6</v>
@@ -1573,28 +1573,28 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.8126611</v>
       </c>
       <c r="N2">
-        <v>173.6333333333333</v>
+        <v>171.8206722333333</v>
       </c>
       <c r="O2">
-        <v>39.93566666666667</v>
+        <v>39.51875461366667</v>
       </c>
       <c r="P2">
-        <v>133.6976666666667</v>
+        <v>132.3019176196667</v>
       </c>
       <c r="Q2">
-        <v>221.8976666666667</v>
+        <v>220.5019176196666</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07459822422242116</v>
+        <v>0.07482221041081777</v>
       </c>
       <c r="T2">
-        <v>0.4454993697880389</v>
+        <v>0.4489643648863904</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>95.78918714222604</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1619,22 +1619,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0744612983067096</v>
+        <v>0.07432437239099803</v>
       </c>
       <c r="C3">
-        <v>3790.602025052492</v>
+        <v>3771.447913219055</v>
       </c>
       <c r="D3">
-        <v>3517.039025052492</v>
+        <v>3533.921913219056</v>
       </c>
       <c r="E3">
-        <v>-1484.663</v>
+        <v>-1448.626</v>
       </c>
       <c r="F3">
-        <v>36.037</v>
+        <v>72.074</v>
       </c>
       <c r="G3">
         <v>309.6</v>
@@ -1655,28 +1655,28 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M3">
-        <v>1.8126611</v>
+        <v>3.6253222</v>
       </c>
       <c r="N3">
-        <v>171.8206722333333</v>
+        <v>170.0080111333333</v>
       </c>
       <c r="O3">
-        <v>39.51875461366667</v>
+        <v>39.10184256066667</v>
       </c>
       <c r="P3">
-        <v>132.3019176196667</v>
+        <v>130.9061685726667</v>
       </c>
       <c r="Q3">
-        <v>220.5019176196666</v>
+        <v>219.1061685726667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07482221041081777</v>
+        <v>0.07505076774591635</v>
       </c>
       <c r="T3">
-        <v>0.4489643648863904</v>
+        <v>0.4525000741704224</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>95.78918714222604</v>
+        <v>47.89459357111303</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1701,22 +1701,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07432437239099803</v>
+        <v>0.07418744647528647</v>
       </c>
       <c r="C4">
-        <v>3771.447913219055</v>
+        <v>3752.456669498752</v>
       </c>
       <c r="D4">
-        <v>3533.921913219056</v>
+        <v>3550.967669498752</v>
       </c>
       <c r="E4">
-        <v>-1448.626</v>
+        <v>-1412.589</v>
       </c>
       <c r="F4">
-        <v>72.074</v>
+        <v>108.111</v>
       </c>
       <c r="G4">
         <v>309.6</v>
@@ -1737,28 +1737,28 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M4">
-        <v>3.6253222</v>
+        <v>5.437983299999999</v>
       </c>
       <c r="N4">
-        <v>170.0080111333333</v>
+        <v>168.1953500333333</v>
       </c>
       <c r="O4">
-        <v>39.10184256066667</v>
+        <v>38.68493050766667</v>
       </c>
       <c r="P4">
-        <v>130.9061685726667</v>
+        <v>129.5104195256667</v>
       </c>
       <c r="Q4">
-        <v>219.1061685726667</v>
+        <v>217.7104195256667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07505076774591635</v>
+        <v>0.0752840376033881</v>
       </c>
       <c r="T4">
-        <v>0.4525000741704224</v>
+        <v>0.4561086846768056</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>47.89459357111303</v>
+        <v>31.92972904740869</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1783,22 +1783,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07418744647528647</v>
+        <v>0.07405052055957488</v>
       </c>
       <c r="C5">
-        <v>3752.456669498752</v>
+        <v>3733.630662081455</v>
       </c>
       <c r="D5">
-        <v>3550.967669498752</v>
+        <v>3568.178662081456</v>
       </c>
       <c r="E5">
-        <v>-1412.589</v>
+        <v>-1376.552</v>
       </c>
       <c r="F5">
-        <v>108.111</v>
+        <v>144.148</v>
       </c>
       <c r="G5">
         <v>309.6</v>
@@ -1819,28 +1819,28 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M5">
-        <v>5.437983299999999</v>
+        <v>7.2506444</v>
       </c>
       <c r="N5">
-        <v>168.1953500333333</v>
+        <v>166.3826889333333</v>
       </c>
       <c r="O5">
-        <v>38.68493050766667</v>
+        <v>38.26801845466667</v>
       </c>
       <c r="P5">
-        <v>129.5104195256667</v>
+        <v>128.1146704786667</v>
       </c>
       <c r="Q5">
-        <v>217.7104195256667</v>
+        <v>216.3146704786666</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0752840376033881</v>
+        <v>0.07552216724955718</v>
       </c>
       <c r="T5">
-        <v>0.4561086846768056</v>
+        <v>0.4597924745687385</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>31.92972904740869</v>
+        <v>23.94729678555651</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1865,22 +1865,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07405052055957488</v>
+        <v>0.07391359464386331</v>
       </c>
       <c r="C6">
-        <v>3733.630662081455</v>
+        <v>3714.972305293651</v>
       </c>
       <c r="D6">
-        <v>3568.178662081456</v>
+        <v>3585.557305293651</v>
       </c>
       <c r="E6">
-        <v>-1376.552</v>
+        <v>-1340.515</v>
       </c>
       <c r="F6">
-        <v>144.148</v>
+        <v>180.185</v>
       </c>
       <c r="G6">
         <v>309.6</v>
@@ -1901,28 +1901,28 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M6">
-        <v>7.2506444</v>
+        <v>9.0633055</v>
       </c>
       <c r="N6">
-        <v>166.3826889333333</v>
+        <v>164.5700278333333</v>
       </c>
       <c r="O6">
-        <v>38.26801845466667</v>
+        <v>37.85110640166666</v>
       </c>
       <c r="P6">
-        <v>128.1146704786667</v>
+        <v>126.7189214316666</v>
       </c>
       <c r="Q6">
-        <v>216.3146704786666</v>
+        <v>214.9189214316667</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07552216724955718</v>
+        <v>0.07576531015143508</v>
       </c>
       <c r="T6">
-        <v>0.4597924745687385</v>
+        <v>0.4635538179320805</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>23.94729678555651</v>
+        <v>19.15783742844521</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1947,22 +1947,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07391359464386331</v>
+        <v>0.07377666872815174</v>
       </c>
       <c r="C7">
-        <v>3714.972305293651</v>
+        <v>3696.484060727483</v>
       </c>
       <c r="D7">
-        <v>3585.557305293651</v>
+        <v>3603.106060727483</v>
       </c>
       <c r="E7">
-        <v>-1340.515</v>
+        <v>-1304.478</v>
       </c>
       <c r="F7">
-        <v>180.185</v>
+        <v>216.222</v>
       </c>
       <c r="G7">
         <v>309.6</v>
@@ -1983,28 +1983,28 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M7">
-        <v>9.0633055</v>
+        <v>10.8759666</v>
       </c>
       <c r="N7">
-        <v>164.5700278333333</v>
+        <v>162.7573667333333</v>
       </c>
       <c r="O7">
-        <v>37.85110640166666</v>
+        <v>37.43419434866667</v>
       </c>
       <c r="P7">
-        <v>126.7189214316666</v>
+        <v>125.3231723846667</v>
       </c>
       <c r="Q7">
-        <v>214.9189214316667</v>
+        <v>213.5231723846667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07576531015143508</v>
+        <v>0.07601362630654442</v>
       </c>
       <c r="T7">
-        <v>0.4635538179320805</v>
+        <v>0.4673951898776213</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>19.15783742844521</v>
+        <v>15.96486452370434</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07377666872815174</v>
+        <v>0.07363974281244018</v>
       </c>
       <c r="C8">
-        <v>3696.484060727483</v>
+        <v>3678.168438403088</v>
       </c>
       <c r="D8">
-        <v>3603.106060727483</v>
+        <v>3620.827438403088</v>
       </c>
       <c r="E8">
-        <v>-1304.478</v>
+        <v>-1268.441</v>
       </c>
       <c r="F8">
-        <v>216.222</v>
+        <v>252.259</v>
       </c>
       <c r="G8">
         <v>309.6</v>
@@ -2065,28 +2065,28 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M8">
-        <v>10.8759666</v>
+        <v>12.6886277</v>
       </c>
       <c r="N8">
-        <v>162.7573667333333</v>
+        <v>160.9447056333333</v>
       </c>
       <c r="O8">
-        <v>37.43419434866667</v>
+        <v>37.01728229566667</v>
       </c>
       <c r="P8">
-        <v>125.3231723846667</v>
+        <v>123.9274233376667</v>
       </c>
       <c r="Q8">
-        <v>213.5231723846667</v>
+        <v>212.1274233376667</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07601362630654442</v>
+        <v>0.0762672825940217</v>
       </c>
       <c r="T8">
-        <v>0.4673951898776212</v>
+        <v>0.4713191719725284</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>15.96486452370434</v>
+        <v>13.68416959174658</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2111,22 +2111,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07363974281244018</v>
+        <v>0.07359521689672863</v>
       </c>
       <c r="C9">
-        <v>3678.168438403088</v>
+        <v>3647.931740589159</v>
       </c>
       <c r="D9">
-        <v>3620.827438403088</v>
+        <v>3626.627740589159</v>
       </c>
       <c r="E9">
-        <v>-1268.441</v>
+        <v>-1232.404</v>
       </c>
       <c r="F9">
-        <v>252.259</v>
+        <v>288.296</v>
       </c>
       <c r="G9">
         <v>309.6</v>
@@ -2147,45 +2147,45 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M9">
-        <v>12.6886277</v>
+        <v>14.9337328</v>
       </c>
       <c r="N9">
-        <v>160.9447056333333</v>
+        <v>158.6996005333333</v>
       </c>
       <c r="O9">
-        <v>37.01728229566666</v>
+        <v>36.50090812266667</v>
       </c>
       <c r="P9">
-        <v>123.9274233376667</v>
+        <v>122.1986924106667</v>
       </c>
       <c r="Q9">
-        <v>212.1274233376666</v>
+        <v>210.3986924106667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0762672825940217</v>
+        <v>0.07652645314861806</v>
       </c>
       <c r="T9">
-        <v>0.4713191719725284</v>
+        <v>0.4753284580260206</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.23</v>
       </c>
       <c r="W9">
-        <v>0.038731</v>
+        <v>0.039886</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>13.68416959174658</v>
+        <v>11.62692112271711</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2193,22 +2193,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07359521689672863</v>
+        <v>0.07346984098101704</v>
       </c>
       <c r="C10">
-        <v>3647.931740589159</v>
+        <v>3628.32749761994</v>
       </c>
       <c r="D10">
-        <v>3626.627740589159</v>
+        <v>3643.060497619941</v>
       </c>
       <c r="E10">
-        <v>-1232.404</v>
+        <v>-1196.367</v>
       </c>
       <c r="F10">
-        <v>288.296</v>
+        <v>324.333</v>
       </c>
       <c r="G10">
         <v>309.6</v>
@@ -2229,28 +2229,28 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M10">
-        <v>14.9337328</v>
+        <v>16.8004494</v>
       </c>
       <c r="N10">
-        <v>158.6996005333333</v>
+        <v>156.8328839333333</v>
       </c>
       <c r="O10">
-        <v>36.50090812266667</v>
+        <v>36.07156330466667</v>
       </c>
       <c r="P10">
-        <v>122.1986924106667</v>
+        <v>120.7613206286667</v>
       </c>
       <c r="Q10">
-        <v>210.3986924106667</v>
+        <v>208.9613206286667</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07652645314861806</v>
+        <v>0.07679131975935939</v>
       </c>
       <c r="T10">
-        <v>0.4753284580260206</v>
+        <v>0.4794258602565127</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>11.62692112271711</v>
+        <v>10.33504099797077</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2275,22 +2275,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07346984098101704</v>
+        <v>0.07347536506530547</v>
       </c>
       <c r="C11">
-        <v>3628.32749761994</v>
+        <v>3591.56333202667</v>
       </c>
       <c r="D11">
-        <v>3643.060497619941</v>
+        <v>3642.33333202667</v>
       </c>
       <c r="E11">
-        <v>-1196.367</v>
+        <v>-1160.33</v>
       </c>
       <c r="F11">
-        <v>324.333</v>
+        <v>360.3699999999999</v>
       </c>
       <c r="G11">
         <v>309.6</v>
@@ -2311,45 +2311,45 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M11">
-        <v>16.8004494</v>
+        <v>19.279795</v>
       </c>
       <c r="N11">
-        <v>156.8328839333333</v>
+        <v>154.3535383333333</v>
       </c>
       <c r="O11">
-        <v>36.07156330466667</v>
+        <v>35.50131381666667</v>
       </c>
       <c r="P11">
-        <v>120.7613206286667</v>
+        <v>118.8522245166667</v>
       </c>
       <c r="Q11">
-        <v>208.9613206286667</v>
+        <v>207.0522245166667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07679131975935939</v>
+        <v>0.07706207229478386</v>
       </c>
       <c r="T11">
-        <v>0.4794258602565127</v>
+        <v>0.4836143158699044</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.23</v>
       </c>
       <c r="W11">
-        <v>0.039886</v>
+        <v>0.041195</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>10.33504099797077</v>
+        <v>9.005974043465367</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2357,22 +2357,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07347536506530547</v>
+        <v>0.07336307914959392</v>
       </c>
       <c r="C12">
-        <v>3591.56333202667</v>
+        <v>3570.36439606493</v>
       </c>
       <c r="D12">
-        <v>3642.33333202667</v>
+        <v>3657.17139606493</v>
       </c>
       <c r="E12">
-        <v>-1160.33</v>
+        <v>-1124.293</v>
       </c>
       <c r="F12">
-        <v>360.37</v>
+        <v>396.407</v>
       </c>
       <c r="G12">
         <v>309.6</v>
@@ -2393,28 +2393,28 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M12">
-        <v>19.279795</v>
+        <v>21.2077745</v>
       </c>
       <c r="N12">
-        <v>154.3535383333333</v>
+        <v>152.4255588333333</v>
       </c>
       <c r="O12">
-        <v>35.50131381666667</v>
+        <v>35.05787853166667</v>
       </c>
       <c r="P12">
-        <v>118.8522245166667</v>
+        <v>117.3676803016667</v>
       </c>
       <c r="Q12">
-        <v>207.0522245166667</v>
+        <v>205.5676803016667</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07706207229478386</v>
+        <v>0.07733890915684709</v>
       </c>
       <c r="T12">
-        <v>0.4836143158699044</v>
+        <v>0.4878968940813501</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>9.005974043465365</v>
+        <v>8.187249130423059</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2439,22 +2439,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07336307914959392</v>
+        <v>0.07332471323388236</v>
       </c>
       <c r="C13">
-        <v>3570.36439606493</v>
+        <v>3539.425023361967</v>
       </c>
       <c r="D13">
-        <v>3657.17139606493</v>
+        <v>3662.269023361967</v>
       </c>
       <c r="E13">
-        <v>-1124.293</v>
+        <v>-1088.256</v>
       </c>
       <c r="F13">
-        <v>396.407</v>
+        <v>432.444</v>
       </c>
       <c r="G13">
         <v>309.6</v>
@@ -2475,45 +2475,45 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M13">
-        <v>21.2077745</v>
+        <v>23.4817092</v>
       </c>
       <c r="N13">
-        <v>152.4255588333333</v>
+        <v>150.1516241333333</v>
       </c>
       <c r="O13">
-        <v>35.05787853166667</v>
+        <v>34.53487355066667</v>
       </c>
       <c r="P13">
-        <v>117.3676803016667</v>
+        <v>115.6167505826666</v>
       </c>
       <c r="Q13">
-        <v>205.5676803016667</v>
+        <v>203.8167505826667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07733890915684709</v>
+        <v>0.07762203776577539</v>
       </c>
       <c r="T13">
-        <v>0.4878968940813501</v>
+        <v>0.492276803615783</v>
       </c>
       <c r="U13">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V13">
         <v>0.23</v>
       </c>
       <c r="W13">
-        <v>0.041195</v>
+        <v>0.041811</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y13">
-        <v>8.187249130423059</v>
+        <v>7.394407785840961</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2521,22 +2521,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07332471323388236</v>
+        <v>0.07321858731817077</v>
       </c>
       <c r="C14">
-        <v>3539.425023361967</v>
+        <v>3517.563139285205</v>
       </c>
       <c r="D14">
-        <v>3662.269023361967</v>
+        <v>3676.444139285205</v>
       </c>
       <c r="E14">
-        <v>-1088.256</v>
+        <v>-1052.219</v>
       </c>
       <c r="F14">
-        <v>432.444</v>
+        <v>468.481</v>
       </c>
       <c r="G14">
         <v>309.6</v>
@@ -2557,28 +2557,28 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M14">
-        <v>23.4817092</v>
+        <v>25.4385183</v>
       </c>
       <c r="N14">
-        <v>150.1516241333333</v>
+        <v>148.1948150333333</v>
       </c>
       <c r="O14">
-        <v>34.53487355066667</v>
+        <v>34.08480745766666</v>
       </c>
       <c r="P14">
-        <v>115.6167505826666</v>
+        <v>114.1100075756667</v>
       </c>
       <c r="Q14">
-        <v>203.8167505826667</v>
+        <v>202.3100075756666</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07762203776577539</v>
+        <v>0.0779116750783572</v>
       </c>
       <c r="T14">
-        <v>0.492276803615783</v>
+        <v>0.4967574007257201</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>7.394407785840961</v>
+        <v>6.825607186930117</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2603,22 +2603,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07321858731817077</v>
+        <v>0.07311246140245921</v>
       </c>
       <c r="C15">
-        <v>3517.563139285205</v>
+        <v>3495.811413508381</v>
       </c>
       <c r="D15">
-        <v>3676.444139285205</v>
+        <v>3690.729413508381</v>
       </c>
       <c r="E15">
-        <v>-1052.219</v>
+        <v>-1016.182</v>
       </c>
       <c r="F15">
-        <v>468.481</v>
+        <v>504.518</v>
       </c>
       <c r="G15">
         <v>309.6</v>
@@ -2639,28 +2639,28 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M15">
-        <v>25.4385183</v>
+        <v>27.3953274</v>
       </c>
       <c r="N15">
-        <v>148.1948150333333</v>
+        <v>146.2380059333333</v>
       </c>
       <c r="O15">
-        <v>34.08480745766666</v>
+        <v>33.63474136466667</v>
       </c>
       <c r="P15">
-        <v>114.1100075756667</v>
+        <v>112.6032645686666</v>
       </c>
       <c r="Q15">
-        <v>202.3100075756666</v>
+        <v>200.8032645686666</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0779116750783572</v>
+        <v>0.07820804814239442</v>
       </c>
       <c r="T15">
-        <v>0.4967574007257201</v>
+        <v>0.5013421977684466</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>6.825607186930117</v>
+        <v>6.338063816435109</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2685,22 +2685,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07311246140245921</v>
+        <v>0.07312183548674764</v>
       </c>
       <c r="C16">
-        <v>3495.811413508381</v>
+        <v>3458.50812930779</v>
       </c>
       <c r="D16">
-        <v>3690.729413508381</v>
+        <v>3689.46312930779</v>
       </c>
       <c r="E16">
-        <v>-1016.182</v>
+        <v>-980.145</v>
       </c>
       <c r="F16">
-        <v>504.518</v>
+        <v>540.5550000000001</v>
       </c>
       <c r="G16">
         <v>309.6</v>
@@ -2721,45 +2721,45 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M16">
-        <v>27.3953274</v>
+        <v>29.89269150000001</v>
       </c>
       <c r="N16">
-        <v>146.2380059333333</v>
+        <v>143.7406418333333</v>
       </c>
       <c r="O16">
-        <v>33.63474136466667</v>
+        <v>33.06034762166666</v>
       </c>
       <c r="P16">
-        <v>112.6032645686666</v>
+        <v>110.6802942116666</v>
       </c>
       <c r="Q16">
-        <v>200.8032645686666</v>
+        <v>198.8802942116666</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07820804814239442</v>
+        <v>0.07851139469029134</v>
       </c>
       <c r="T16">
-        <v>0.5013421977684466</v>
+        <v>0.506034872388649</v>
       </c>
       <c r="U16">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V16">
         <v>0.23</v>
       </c>
       <c r="W16">
-        <v>0.041811</v>
+        <v>0.042581</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y16">
-        <v>6.338063816435109</v>
+        <v>5.808554687467112</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2767,22 +2767,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07312183548674762</v>
+        <v>0.07302340957103606</v>
       </c>
       <c r="C17">
-        <v>3458.508129307791</v>
+        <v>3435.810339667853</v>
       </c>
       <c r="D17">
-        <v>3689.463129307791</v>
+        <v>3702.802339667853</v>
       </c>
       <c r="E17">
-        <v>-980.1450000000001</v>
+        <v>-944.1080000000001</v>
       </c>
       <c r="F17">
-        <v>540.5549999999999</v>
+        <v>576.592</v>
       </c>
       <c r="G17">
         <v>309.6</v>
@@ -2803,28 +2803,28 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M17">
-        <v>29.8926915</v>
+        <v>31.8855376</v>
       </c>
       <c r="N17">
-        <v>143.7406418333333</v>
+        <v>141.7477957333333</v>
       </c>
       <c r="O17">
-        <v>33.06034762166666</v>
+        <v>32.60199301866667</v>
       </c>
       <c r="P17">
-        <v>110.6802942116666</v>
+        <v>109.1458027146667</v>
       </c>
       <c r="Q17">
-        <v>198.8802942116666</v>
+        <v>197.3458027146667</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07851139469029134</v>
+        <v>0.07882196377504294</v>
       </c>
       <c r="T17">
-        <v>0.506034872388649</v>
+        <v>0.5108392773569513</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.808554687467113</v>
+        <v>5.445520019500419</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2849,22 +2849,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07302340957103606</v>
+        <v>0.0729249836553245</v>
       </c>
       <c r="C18">
-        <v>3435.810339667853</v>
+        <v>3413.209355542067</v>
       </c>
       <c r="D18">
-        <v>3702.802339667853</v>
+        <v>3716.238355542067</v>
       </c>
       <c r="E18">
-        <v>-944.1080000000001</v>
+        <v>-908.071</v>
       </c>
       <c r="F18">
-        <v>576.592</v>
+        <v>612.629</v>
       </c>
       <c r="G18">
         <v>309.6</v>
@@ -2885,28 +2885,28 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M18">
-        <v>31.8855376</v>
+        <v>33.8783837</v>
       </c>
       <c r="N18">
-        <v>141.7477957333333</v>
+        <v>139.7549496333333</v>
       </c>
       <c r="O18">
-        <v>32.60199301866667</v>
+        <v>32.14363841566666</v>
       </c>
       <c r="P18">
-        <v>109.1458027146667</v>
+        <v>107.6113112176667</v>
       </c>
       <c r="Q18">
-        <v>197.3458027146667</v>
+        <v>195.8113112176667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07882196377504294</v>
+        <v>0.07914001645219819</v>
       </c>
       <c r="T18">
-        <v>0.5108392773569513</v>
+        <v>0.5157594511196706</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.445520019500419</v>
+        <v>5.125195312470982</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2931,22 +2931,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0729249836553245</v>
+        <v>0.07282655773961291</v>
       </c>
       <c r="C19">
-        <v>3413.209355542067</v>
+        <v>3390.706234575823</v>
       </c>
       <c r="D19">
-        <v>3716.238355542067</v>
+        <v>3729.772234575823</v>
       </c>
       <c r="E19">
-        <v>-908.071</v>
+        <v>-872.034</v>
       </c>
       <c r="F19">
-        <v>612.629</v>
+        <v>648.6660000000001</v>
       </c>
       <c r="G19">
         <v>309.6</v>
@@ -2967,28 +2967,28 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M19">
-        <v>33.8783837</v>
+        <v>35.8712298</v>
       </c>
       <c r="N19">
-        <v>139.7549496333333</v>
+        <v>137.7621035333333</v>
       </c>
       <c r="O19">
-        <v>32.14363841566666</v>
+        <v>31.68528381266666</v>
       </c>
       <c r="P19">
-        <v>107.6113112176667</v>
+        <v>106.0768197206666</v>
       </c>
       <c r="Q19">
-        <v>195.8113112176667</v>
+        <v>194.2768197206667</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07914001645219819</v>
+        <v>0.07946582651172307</v>
       </c>
       <c r="T19">
-        <v>0.5157594511196706</v>
+        <v>0.5207996291205049</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.125195312470982</v>
+        <v>4.840462239555928</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3013,22 +3013,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07282655773961293</v>
+        <v>0.07272813182390137</v>
       </c>
       <c r="C20">
-        <v>3390.706234575821</v>
+        <v>3368.302049877841</v>
       </c>
       <c r="D20">
-        <v>3729.772234575821</v>
+        <v>3743.405049877841</v>
       </c>
       <c r="E20">
-        <v>-872.0340000000001</v>
+        <v>-835.9970000000001</v>
       </c>
       <c r="F20">
-        <v>648.6659999999999</v>
+        <v>684.703</v>
       </c>
       <c r="G20">
         <v>309.6</v>
@@ -3049,28 +3049,28 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M20">
-        <v>35.87122979999999</v>
+        <v>37.8640759</v>
       </c>
       <c r="N20">
-        <v>137.7621035333333</v>
+        <v>135.7692574333333</v>
       </c>
       <c r="O20">
-        <v>31.68528381266667</v>
+        <v>31.22692920966667</v>
       </c>
       <c r="P20">
-        <v>106.0768197206667</v>
+        <v>104.5423282236667</v>
       </c>
       <c r="Q20">
-        <v>194.2768197206667</v>
+        <v>192.7423282236667</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07946582651172307</v>
+        <v>0.07979968126407574</v>
       </c>
       <c r="T20">
-        <v>0.5207996291205049</v>
+        <v>0.5259642559608662</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>4.840462239555928</v>
+        <v>4.585701069052984</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07272813182390137</v>
+        <v>0.07301470590818979</v>
       </c>
       <c r="C21">
-        <v>3368.302049877841</v>
+        <v>3292.846550265594</v>
       </c>
       <c r="D21">
-        <v>3743.405049877841</v>
+        <v>3703.986550265593</v>
       </c>
       <c r="E21">
-        <v>-835.9970000000001</v>
+        <v>-799.96</v>
       </c>
       <c r="F21">
-        <v>684.703</v>
+        <v>720.74</v>
       </c>
       <c r="G21">
         <v>309.6</v>
@@ -3131,45 +3131,45 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M21">
-        <v>37.8640759</v>
+        <v>41.65877200000001</v>
       </c>
       <c r="N21">
-        <v>135.7692574333333</v>
+        <v>131.9745613333333</v>
       </c>
       <c r="O21">
-        <v>31.22692920966667</v>
+        <v>30.35414910666667</v>
       </c>
       <c r="P21">
-        <v>104.5423282236667</v>
+        <v>101.6204122266667</v>
       </c>
       <c r="Q21">
-        <v>192.7423282236667</v>
+        <v>189.8204122266667</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07979968126407574</v>
+        <v>0.08014188238523723</v>
       </c>
       <c r="T21">
-        <v>0.5259642559608662</v>
+        <v>0.5312579984722363</v>
       </c>
       <c r="U21">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V21">
         <v>0.23</v>
       </c>
       <c r="W21">
-        <v>0.042581</v>
+        <v>0.044506</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>4.585701069052984</v>
+        <v>4.167989717347725</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3177,22 +3177,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07301470590818979</v>
+        <v>0.07350147999247823</v>
       </c>
       <c r="C22">
-        <v>3292.846550265594</v>
+        <v>3191.722606834708</v>
       </c>
       <c r="D22">
-        <v>3703.986550265593</v>
+        <v>3638.899606834708</v>
       </c>
       <c r="E22">
-        <v>-799.96</v>
+        <v>-763.923</v>
       </c>
       <c r="F22">
-        <v>720.74</v>
+        <v>756.777</v>
       </c>
       <c r="G22">
         <v>309.6</v>
@@ -3213,45 +3213,45 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M22">
-        <v>41.65877200000001</v>
+        <v>46.3904301</v>
       </c>
       <c r="N22">
-        <v>131.9745613333333</v>
+        <v>127.2429032333333</v>
       </c>
       <c r="O22">
-        <v>30.35414910666667</v>
+        <v>29.26586774366666</v>
       </c>
       <c r="P22">
-        <v>101.6204122266667</v>
+        <v>97.97703548966666</v>
       </c>
       <c r="Q22">
-        <v>189.8204122266667</v>
+        <v>186.1770354896667</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08014188238523723</v>
+        <v>0.08049274682592181</v>
       </c>
       <c r="T22">
-        <v>0.5312579984722363</v>
+        <v>0.5366857597813628</v>
       </c>
       <c r="U22">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V22">
         <v>0.23</v>
       </c>
       <c r="W22">
-        <v>0.044506</v>
+        <v>0.047201</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.167989717347725</v>
+        <v>3.74286965995026</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3259,22 +3259,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07350147999247823</v>
+        <v>0.07344925407676665</v>
       </c>
       <c r="C23">
-        <v>3191.722606834708</v>
+        <v>3162.559024237643</v>
       </c>
       <c r="D23">
-        <v>3638.899606834708</v>
+        <v>3645.773024237643</v>
       </c>
       <c r="E23">
-        <v>-763.9230000000001</v>
+        <v>-727.8860000000001</v>
       </c>
       <c r="F23">
-        <v>756.7769999999999</v>
+        <v>792.814</v>
       </c>
       <c r="G23">
         <v>309.6</v>
@@ -3295,28 +3295,28 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M23">
-        <v>46.3904301</v>
+        <v>48.5994982</v>
       </c>
       <c r="N23">
-        <v>127.2429032333333</v>
+        <v>125.0338351333333</v>
       </c>
       <c r="O23">
-        <v>29.26586774366666</v>
+        <v>28.75778208066667</v>
       </c>
       <c r="P23">
-        <v>97.97703548966666</v>
+        <v>96.27605305266667</v>
       </c>
       <c r="Q23">
-        <v>186.1770354896667</v>
+        <v>184.4760530526667</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08049274682592181</v>
+        <v>0.08085260779072648</v>
       </c>
       <c r="T23">
-        <v>0.5366857597813628</v>
+        <v>0.5422526944573899</v>
       </c>
       <c r="U23">
         <v>0.0613</v>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.74286965995026</v>
+        <v>3.572739220861612</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3341,22 +3341,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07344925407676665</v>
+        <v>0.07389290816105509</v>
       </c>
       <c r="C24">
-        <v>3162.559024237643</v>
+        <v>3068.946564861247</v>
       </c>
       <c r="D24">
-        <v>3645.773024237643</v>
+        <v>3588.197564861247</v>
       </c>
       <c r="E24">
-        <v>-727.8860000000001</v>
+        <v>-691.849</v>
       </c>
       <c r="F24">
-        <v>792.814</v>
+        <v>828.851</v>
       </c>
       <c r="G24">
         <v>309.6</v>
@@ -3377,45 +3377,45 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M24">
-        <v>48.5994982</v>
+        <v>53.12934910000001</v>
       </c>
       <c r="N24">
-        <v>125.0338351333333</v>
+        <v>120.5039842333333</v>
       </c>
       <c r="O24">
-        <v>28.75778208066667</v>
+        <v>27.71591637366666</v>
       </c>
       <c r="P24">
-        <v>96.27605305266667</v>
+        <v>92.78806785966665</v>
       </c>
       <c r="Q24">
-        <v>184.4760530526667</v>
+        <v>180.9880678596667</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08085260779072648</v>
+        <v>0.08122181579357804</v>
       </c>
       <c r="T24">
-        <v>0.5422526944573899</v>
+        <v>0.5479642248392879</v>
       </c>
       <c r="U24">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V24">
         <v>0.23</v>
       </c>
       <c r="W24">
-        <v>0.047201</v>
+        <v>0.04935700000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>3.572739220861612</v>
+        <v>3.268124610495808</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3423,22 +3423,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07389290816105509</v>
+        <v>0.07386224224534352</v>
       </c>
       <c r="C25">
-        <v>3068.946564861247</v>
+        <v>3036.830682893032</v>
       </c>
       <c r="D25">
-        <v>3588.197564861247</v>
+        <v>3592.118682893032</v>
       </c>
       <c r="E25">
-        <v>-691.849</v>
+        <v>-655.812</v>
       </c>
       <c r="F25">
-        <v>828.851</v>
+        <v>864.888</v>
       </c>
       <c r="G25">
         <v>309.6</v>
@@ -3459,28 +3459,28 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M25">
-        <v>53.12934910000001</v>
+        <v>55.4393208</v>
       </c>
       <c r="N25">
-        <v>120.5039842333333</v>
+        <v>118.1940125333333</v>
       </c>
       <c r="O25">
-        <v>27.71591637366666</v>
+        <v>27.18462288266667</v>
       </c>
       <c r="P25">
-        <v>92.78806785966665</v>
+        <v>91.00938965066666</v>
       </c>
       <c r="Q25">
-        <v>180.9880678596667</v>
+        <v>179.2093896506667</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08122181579357804</v>
+        <v>0.08160073979650462</v>
       </c>
       <c r="T25">
-        <v>0.5479642248392879</v>
+        <v>0.5538260586522883</v>
       </c>
       <c r="U25">
         <v>0.0641</v>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.268124610495808</v>
+        <v>3.131952751725149</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3505,22 +3505,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07386224224534352</v>
+        <v>0.07383157632963194</v>
       </c>
       <c r="C26">
-        <v>3036.830682893032</v>
+        <v>3004.723380155156</v>
       </c>
       <c r="D26">
-        <v>3592.118682893032</v>
+        <v>3596.048380155156</v>
       </c>
       <c r="E26">
-        <v>-655.8120000000001</v>
+        <v>-619.7750000000001</v>
       </c>
       <c r="F26">
-        <v>864.8879999999999</v>
+        <v>900.925</v>
       </c>
       <c r="G26">
         <v>309.6</v>
@@ -3541,28 +3541,28 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M26">
-        <v>55.4393208</v>
+        <v>57.7492925</v>
       </c>
       <c r="N26">
-        <v>118.1940125333333</v>
+        <v>115.8840408333333</v>
       </c>
       <c r="O26">
-        <v>27.18462288266667</v>
+        <v>26.65332939166667</v>
       </c>
       <c r="P26">
-        <v>91.00938965066666</v>
+        <v>89.23071144166667</v>
       </c>
       <c r="Q26">
-        <v>179.2093896506667</v>
+        <v>177.4307114416667</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08160073979650462</v>
+        <v>0.08198976843950925</v>
       </c>
       <c r="T26">
-        <v>0.5538260586522883</v>
+        <v>0.5598442080336355</v>
       </c>
       <c r="U26">
         <v>0.0641</v>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.13195275172515</v>
+        <v>3.006674641656144</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3587,22 +3587,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07383157632963194</v>
+        <v>0.07536247041392037</v>
       </c>
       <c r="C27">
-        <v>3004.723380155156</v>
+        <v>2782.464825768339</v>
       </c>
       <c r="D27">
-        <v>3596.048380155156</v>
+        <v>3409.826825768339</v>
       </c>
       <c r="E27">
-        <v>-619.7750000000001</v>
+        <v>-583.7380000000001</v>
       </c>
       <c r="F27">
-        <v>900.925</v>
+        <v>936.962</v>
       </c>
       <c r="G27">
         <v>309.6</v>
@@ -3623,45 +3623,45 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M27">
-        <v>57.7492925</v>
+        <v>67.3675678</v>
       </c>
       <c r="N27">
-        <v>115.8840408333333</v>
+        <v>106.2657655333333</v>
       </c>
       <c r="O27">
-        <v>26.65332939166667</v>
+        <v>24.44112607266667</v>
       </c>
       <c r="P27">
-        <v>89.23071144166667</v>
+        <v>81.82463946066666</v>
       </c>
       <c r="Q27">
-        <v>177.4307114416667</v>
+        <v>170.0246394606667</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08198976843950925</v>
+        <v>0.08238931137016267</v>
       </c>
       <c r="T27">
-        <v>0.5598442080336355</v>
+        <v>0.5660250101009651</v>
       </c>
       <c r="U27">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V27">
         <v>0.23</v>
       </c>
       <c r="W27">
-        <v>0.04935700000000001</v>
+        <v>0.055363</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.006674641656144</v>
+        <v>2.577402435676672</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3669,22 +3669,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07536247041392037</v>
+        <v>0.07620267449820881</v>
       </c>
       <c r="C28">
-        <v>2782.464825768339</v>
+        <v>2652.194325820971</v>
       </c>
       <c r="D28">
-        <v>3409.826825768339</v>
+        <v>3315.593325820971</v>
       </c>
       <c r="E28">
-        <v>-583.7380000000001</v>
+        <v>-547.701</v>
       </c>
       <c r="F28">
-        <v>936.962</v>
+        <v>972.999</v>
       </c>
       <c r="G28">
         <v>309.6</v>
@@ -3705,45 +3705,45 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M28">
-        <v>67.3675678</v>
+        <v>73.75332420000001</v>
       </c>
       <c r="N28">
-        <v>106.2657655333333</v>
+        <v>99.88000913333332</v>
       </c>
       <c r="O28">
-        <v>24.44112607266667</v>
+        <v>22.97240210066666</v>
       </c>
       <c r="P28">
-        <v>81.82463946066666</v>
+        <v>76.90760703266665</v>
       </c>
       <c r="Q28">
-        <v>170.0246394606667</v>
+        <v>165.1076070326666</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08238931137016267</v>
+        <v>0.08279980068247782</v>
       </c>
       <c r="T28">
-        <v>0.5660250101009651</v>
+        <v>0.5723751492112351</v>
       </c>
       <c r="U28">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V28">
         <v>0.23</v>
       </c>
       <c r="W28">
-        <v>0.055363</v>
+        <v>0.05836600000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.577402435676672</v>
+        <v>2.354244167523683</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3751,22 +3751,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07620267449820881</v>
+        <v>0.07626209858249725</v>
       </c>
       <c r="C29">
-        <v>2652.194325820971</v>
+        <v>2609.689416306261</v>
       </c>
       <c r="D29">
-        <v>3315.593325820971</v>
+        <v>3309.125416306261</v>
       </c>
       <c r="E29">
-        <v>-547.701</v>
+        <v>-511.664</v>
       </c>
       <c r="F29">
-        <v>972.999</v>
+        <v>1009.036</v>
       </c>
       <c r="G29">
         <v>309.6</v>
@@ -3787,28 +3787,28 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M29">
-        <v>73.75332420000001</v>
+        <v>76.48492880000001</v>
       </c>
       <c r="N29">
-        <v>99.88000913333332</v>
+        <v>97.14840453333332</v>
       </c>
       <c r="O29">
-        <v>22.97240210066666</v>
+        <v>22.34413304266667</v>
       </c>
       <c r="P29">
-        <v>76.90760703266665</v>
+        <v>74.80427149066665</v>
       </c>
       <c r="Q29">
-        <v>165.1076070326666</v>
+        <v>163.0042714906667</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08279980068247782</v>
+        <v>0.08322169247569061</v>
       </c>
       <c r="T29">
-        <v>0.5723751492112351</v>
+        <v>0.5789016810745684</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.354244167523683</v>
+        <v>2.270164018683552</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3833,22 +3833,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07626209858249725</v>
+        <v>0.07632152266678567</v>
       </c>
       <c r="C30">
-        <v>2609.689416306261</v>
+        <v>2567.209692271606</v>
       </c>
       <c r="D30">
-        <v>3309.125416306261</v>
+        <v>3302.682692271606</v>
       </c>
       <c r="E30">
-        <v>-511.664</v>
+        <v>-475.627</v>
       </c>
       <c r="F30">
-        <v>1009.036</v>
+        <v>1045.073</v>
       </c>
       <c r="G30">
         <v>309.6</v>
@@ -3869,28 +3869,28 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M30">
-        <v>76.48492880000001</v>
+        <v>79.21653340000002</v>
       </c>
       <c r="N30">
-        <v>97.14840453333332</v>
+        <v>94.41679993333331</v>
       </c>
       <c r="O30">
-        <v>22.34413304266667</v>
+        <v>21.71586398466666</v>
       </c>
       <c r="P30">
-        <v>74.80427149066665</v>
+        <v>72.70093594866665</v>
       </c>
       <c r="Q30">
-        <v>163.0042714906667</v>
+        <v>160.9009359486666</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08322169247569061</v>
+        <v>0.08365546854476855</v>
       </c>
       <c r="T30">
-        <v>0.5789016810745684</v>
+        <v>0.5856120589058827</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.270164018683552</v>
+        <v>2.191882500797911</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3915,22 +3915,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07632152266678567</v>
+        <v>0.0763809467510741</v>
       </c>
       <c r="C31">
-        <v>2567.209692271606</v>
+        <v>2524.755006897736</v>
       </c>
       <c r="D31">
-        <v>3302.682692271606</v>
+        <v>3296.265006897736</v>
       </c>
       <c r="E31">
-        <v>-475.6270000000002</v>
+        <v>-439.5900000000001</v>
       </c>
       <c r="F31">
-        <v>1045.073</v>
+        <v>1081.11</v>
       </c>
       <c r="G31">
         <v>309.6</v>
@@ -3951,28 +3951,28 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M31">
-        <v>79.2165334</v>
+        <v>81.948138</v>
       </c>
       <c r="N31">
-        <v>94.41679993333332</v>
+        <v>91.68519533333333</v>
       </c>
       <c r="O31">
-        <v>21.71586398466667</v>
+        <v>21.08759492666666</v>
       </c>
       <c r="P31">
-        <v>72.70093594866665</v>
+        <v>70.59760040666666</v>
       </c>
       <c r="Q31">
-        <v>160.9009359486666</v>
+        <v>158.7976004066667</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08365546854476855</v>
+        <v>0.08410163821582015</v>
       </c>
       <c r="T31">
-        <v>0.5856120589058827</v>
+        <v>0.5925141618180918</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.191882500797912</v>
+        <v>2.118819750771315</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3997,22 +3997,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0763809467510741</v>
+        <v>0.07644037083536254</v>
       </c>
       <c r="C32">
-        <v>2524.755006897736</v>
+        <v>2482.325214504347</v>
       </c>
       <c r="D32">
-        <v>3296.265006897736</v>
+        <v>3289.872214504347</v>
       </c>
       <c r="E32">
-        <v>-439.5900000000001</v>
+        <v>-403.5530000000001</v>
       </c>
       <c r="F32">
-        <v>1081.11</v>
+        <v>1117.147</v>
       </c>
       <c r="G32">
         <v>309.6</v>
@@ -4033,28 +4033,28 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M32">
-        <v>81.948138</v>
+        <v>84.6797426</v>
       </c>
       <c r="N32">
-        <v>91.68519533333333</v>
+        <v>88.95359073333333</v>
       </c>
       <c r="O32">
-        <v>21.08759492666666</v>
+        <v>20.45932586866667</v>
       </c>
       <c r="P32">
-        <v>70.59760040666666</v>
+        <v>68.49426486466666</v>
       </c>
       <c r="Q32">
-        <v>158.7976004066667</v>
+        <v>156.6942648646666</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08410163821582015</v>
+        <v>0.08456074034110513</v>
       </c>
       <c r="T32">
-        <v>0.5925141618180918</v>
+        <v>0.5996163256842779</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.118819750771315</v>
+        <v>2.050470726552885</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4079,22 +4079,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07644037083536254</v>
+        <v>0.07999867491965096</v>
       </c>
       <c r="C33">
-        <v>2482.325214504347</v>
+        <v>2103.983556058905</v>
       </c>
       <c r="D33">
-        <v>3289.872214504347</v>
+        <v>2947.567556058905</v>
       </c>
       <c r="E33">
-        <v>-403.5530000000001</v>
+        <v>-367.5160000000001</v>
       </c>
       <c r="F33">
-        <v>1117.147</v>
+        <v>1153.184</v>
       </c>
       <c r="G33">
         <v>309.6</v>
@@ -4115,45 +4115,45 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M33">
-        <v>84.6797426</v>
+        <v>103.78656</v>
       </c>
       <c r="N33">
-        <v>88.95359073333333</v>
+        <v>69.84677333333333</v>
       </c>
       <c r="O33">
-        <v>20.45932586866667</v>
+        <v>16.06475786666667</v>
       </c>
       <c r="P33">
-        <v>68.49426486466666</v>
+        <v>53.78201546666666</v>
       </c>
       <c r="Q33">
-        <v>156.6942648646666</v>
+        <v>141.9820154666667</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08456074034110513</v>
+        <v>0.08503334547007493</v>
       </c>
       <c r="T33">
-        <v>0.5996163256842779</v>
+        <v>0.6069273767229988</v>
       </c>
       <c r="U33">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V33">
         <v>0.23</v>
       </c>
       <c r="W33">
-        <v>0.05836600000000001</v>
+        <v>0.0693</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>2.050470726552885</v>
+        <v>1.672984761546517</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07999867491965096</v>
+        <v>0.08016743900393938</v>
       </c>
       <c r="C34">
-        <v>2103.983556058905</v>
+        <v>2053.472287568328</v>
       </c>
       <c r="D34">
-        <v>2947.567556058905</v>
+        <v>2933.093287568328</v>
       </c>
       <c r="E34">
-        <v>-367.5160000000001</v>
+        <v>-331.479</v>
       </c>
       <c r="F34">
-        <v>1153.184</v>
+        <v>1189.221</v>
       </c>
       <c r="G34">
         <v>309.6</v>
@@ -4197,28 +4197,28 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M34">
-        <v>103.78656</v>
+        <v>107.02989</v>
       </c>
       <c r="N34">
-        <v>69.84677333333333</v>
+        <v>66.60344333333333</v>
       </c>
       <c r="O34">
-        <v>16.06475786666667</v>
+        <v>15.31879196666667</v>
       </c>
       <c r="P34">
-        <v>53.78201546666666</v>
+        <v>51.28465136666667</v>
       </c>
       <c r="Q34">
-        <v>141.9820154666667</v>
+        <v>139.4846513666667</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08503334547007493</v>
+        <v>0.08552005821483491</v>
       </c>
       <c r="T34">
-        <v>0.6069273767229988</v>
+        <v>0.6144566680912339</v>
       </c>
       <c r="U34">
         <v>0.09</v>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.672984761546517</v>
+        <v>1.622288253620865</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4243,22 +4243,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08016743900393938</v>
+        <v>0.08033620308822784</v>
       </c>
       <c r="C35">
-        <v>2053.472287568328</v>
+        <v>2003.102478557896</v>
       </c>
       <c r="D35">
-        <v>2933.093287568328</v>
+        <v>2918.760478557896</v>
       </c>
       <c r="E35">
-        <v>-331.479</v>
+        <v>-295.442</v>
       </c>
       <c r="F35">
-        <v>1189.221</v>
+        <v>1225.258</v>
       </c>
       <c r="G35">
         <v>309.6</v>
@@ -4279,28 +4279,28 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M35">
-        <v>107.02989</v>
+        <v>110.27322</v>
       </c>
       <c r="N35">
-        <v>66.60344333333333</v>
+        <v>63.36011333333333</v>
       </c>
       <c r="O35">
-        <v>15.31879196666667</v>
+        <v>14.57282606666667</v>
       </c>
       <c r="P35">
-        <v>51.28465136666667</v>
+        <v>48.78728726666667</v>
       </c>
       <c r="Q35">
-        <v>139.4846513666667</v>
+        <v>136.9872872666667</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08552005821483491</v>
+        <v>0.08602151983064824</v>
       </c>
       <c r="T35">
-        <v>0.6144566680912339</v>
+        <v>0.622214119803961</v>
       </c>
       <c r="U35">
         <v>0.09</v>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.622288253620865</v>
+        <v>1.574573893220252</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4325,22 +4325,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08033620308822784</v>
+        <v>0.08050496717251625</v>
       </c>
       <c r="C36">
-        <v>2003.102478557896</v>
+        <v>1952.872065350719</v>
       </c>
       <c r="D36">
-        <v>2918.760478557896</v>
+        <v>2904.567065350719</v>
       </c>
       <c r="E36">
-        <v>-295.442</v>
+        <v>-259.405</v>
       </c>
       <c r="F36">
-        <v>1225.258</v>
+        <v>1261.295</v>
       </c>
       <c r="G36">
         <v>309.6</v>
@@ -4361,28 +4361,28 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M36">
-        <v>110.27322</v>
+        <v>113.51655</v>
       </c>
       <c r="N36">
-        <v>63.36011333333333</v>
+        <v>60.11678333333332</v>
       </c>
       <c r="O36">
-        <v>14.57282606666667</v>
+        <v>13.82686016666666</v>
       </c>
       <c r="P36">
-        <v>48.78728726666667</v>
+        <v>46.28992316666665</v>
       </c>
       <c r="Q36">
-        <v>136.9872872666667</v>
+        <v>134.4899231666666</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08602151983064824</v>
+        <v>0.0865384110346404</v>
       </c>
       <c r="T36">
-        <v>0.622214119803961</v>
+        <v>0.6302102623386181</v>
       </c>
       <c r="U36">
         <v>0.09</v>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>1.574573893220252</v>
+        <v>1.529586067699673</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4407,22 +4407,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08050496717251625</v>
+        <v>0.09770241109354945</v>
       </c>
       <c r="C37">
-        <v>1952.872065350719</v>
+        <v>954.4302720316466</v>
       </c>
       <c r="D37">
-        <v>2904.567065350719</v>
+        <v>1942.162272031647</v>
       </c>
       <c r="E37">
-        <v>-259.405</v>
+        <v>-223.3679999999999</v>
       </c>
       <c r="F37">
-        <v>1261.295</v>
+        <v>1297.332</v>
       </c>
       <c r="G37">
         <v>309.6</v>
@@ -4443,45 +4443,45 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M37">
-        <v>113.51655</v>
+        <v>190.4483376</v>
       </c>
       <c r="N37">
-        <v>60.11678333333332</v>
+        <v>-16.8150042666667</v>
       </c>
       <c r="O37">
-        <v>13.82686016666666</v>
+        <v>-3.867450981333342</v>
       </c>
       <c r="P37">
-        <v>46.28992316666665</v>
+        <v>-12.94755328533336</v>
       </c>
       <c r="Q37">
-        <v>134.4899231666666</v>
+        <v>75.25244671466663</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0865384110346404</v>
+        <v>0.08740040961567747</v>
       </c>
       <c r="T37">
-        <v>0.6302102623386181</v>
+        <v>0.6435451062388615</v>
       </c>
       <c r="U37">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.23</v>
+        <v>0.2096929128913891</v>
       </c>
       <c r="W37">
-        <v>0.0693</v>
+        <v>0.1160170803875441</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y37">
-        <v>1.529586067699673</v>
+        <v>0.9117083169190829</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4489,22 +4489,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09770241109354945</v>
+        <v>0.09871241109354945</v>
       </c>
       <c r="C38">
-        <v>954.4302720316468</v>
+        <v>881.3209887201976</v>
       </c>
       <c r="D38">
-        <v>1942.162272031647</v>
+        <v>1905.089988720197</v>
       </c>
       <c r="E38">
-        <v>-223.3680000000002</v>
+        <v>-187.3310000000001</v>
       </c>
       <c r="F38">
-        <v>1297.332</v>
+        <v>1333.369</v>
       </c>
       <c r="G38">
         <v>309.6</v>
@@ -4525,37 +4525,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M38">
-        <v>190.4483376</v>
+        <v>195.7385692</v>
       </c>
       <c r="N38">
-        <v>-16.81500426666668</v>
+        <v>-22.10523586666667</v>
       </c>
       <c r="O38">
-        <v>-3.867450981333336</v>
+        <v>-5.084204249333335</v>
       </c>
       <c r="P38">
-        <v>-12.94755328533334</v>
+        <v>-17.02103161733334</v>
       </c>
       <c r="Q38">
-        <v>75.25244671466666</v>
+        <v>71.17896838266667</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08740040961567747</v>
+        <v>0.08806073357783106</v>
       </c>
       <c r="T38">
-        <v>0.6435451062388615</v>
+        <v>0.6537601079251927</v>
       </c>
       <c r="U38">
         <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.2096929128913891</v>
+        <v>0.2040255368672975</v>
       </c>
       <c r="W38">
-        <v>0.1160170803875441</v>
+        <v>0.1168490511878807</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.9117083169190831</v>
+        <v>0.8870675515969457</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4571,22 +4571,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09871241109354945</v>
+        <v>0.09972241109354944</v>
       </c>
       <c r="C39">
-        <v>881.3209887201976</v>
+        <v>809.6004788476653</v>
       </c>
       <c r="D39">
-        <v>1905.089988720197</v>
+        <v>1869.406478847665</v>
       </c>
       <c r="E39">
-        <v>-187.3310000000001</v>
+        <v>-151.2940000000001</v>
       </c>
       <c r="F39">
-        <v>1333.369</v>
+        <v>1369.406</v>
       </c>
       <c r="G39">
         <v>309.6</v>
@@ -4607,37 +4607,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M39">
-        <v>195.7385692</v>
+        <v>201.0288008</v>
       </c>
       <c r="N39">
-        <v>-22.10523586666667</v>
+        <v>-27.39546746666667</v>
       </c>
       <c r="O39">
-        <v>-5.084204249333335</v>
+        <v>-6.300957517333335</v>
       </c>
       <c r="P39">
-        <v>-17.02103161733334</v>
+        <v>-21.09450994933334</v>
       </c>
       <c r="Q39">
-        <v>71.17896838266667</v>
+        <v>67.10549005066666</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08806073357783106</v>
+        <v>0.08874235831295738</v>
       </c>
       <c r="T39">
-        <v>0.6537601079251927</v>
+        <v>0.6643046257949538</v>
       </c>
       <c r="U39">
         <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.2040255368672975</v>
+        <v>0.1986564437918423</v>
       </c>
       <c r="W39">
-        <v>0.1168490511878807</v>
+        <v>0.1176372340513576</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.8870675515969457</v>
+        <v>0.8637236686601839</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4653,22 +4653,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09972241109354944</v>
+        <v>0.1007324110935494</v>
       </c>
       <c r="C40">
-        <v>809.6004788476653</v>
+        <v>739.1921394862686</v>
       </c>
       <c r="D40">
-        <v>1869.406478847665</v>
+        <v>1835.035139486269</v>
       </c>
       <c r="E40">
-        <v>-151.2940000000001</v>
+        <v>-115.2570000000001</v>
       </c>
       <c r="F40">
-        <v>1369.406</v>
+        <v>1405.443</v>
       </c>
       <c r="G40">
         <v>309.6</v>
@@ -4689,37 +4689,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M40">
-        <v>201.0288008</v>
+        <v>206.3190324</v>
       </c>
       <c r="N40">
-        <v>-27.39546746666667</v>
+        <v>-32.6856990666667</v>
       </c>
       <c r="O40">
-        <v>-6.300957517333335</v>
+        <v>-7.517710785333342</v>
       </c>
       <c r="P40">
-        <v>-21.09450994933334</v>
+        <v>-25.16798828133336</v>
       </c>
       <c r="Q40">
-        <v>67.10549005066666</v>
+        <v>63.03201171866665</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08874235831295738</v>
+        <v>0.08944633140005503</v>
       </c>
       <c r="T40">
-        <v>0.6643046257949538</v>
+        <v>0.6751948655620842</v>
       </c>
       <c r="U40">
         <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.1986564437918423</v>
+        <v>0.1935626888228207</v>
       </c>
       <c r="W40">
-        <v>0.1176372340513576</v>
+        <v>0.1183849972808099</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8637236686601839</v>
+        <v>0.8415769079253074</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4735,22 +4735,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1007324110935494</v>
+        <v>0.1017424110935495</v>
       </c>
       <c r="C41">
-        <v>739.1921394862686</v>
+        <v>670.0248997513054</v>
       </c>
       <c r="D41">
-        <v>1835.035139486269</v>
+        <v>1801.904899751305</v>
       </c>
       <c r="E41">
-        <v>-115.2570000000001</v>
+        <v>-79.22000000000003</v>
       </c>
       <c r="F41">
-        <v>1405.443</v>
+        <v>1441.48</v>
       </c>
       <c r="G41">
         <v>309.6</v>
@@ -4771,37 +4771,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M41">
-        <v>206.3190324</v>
+        <v>211.609264</v>
       </c>
       <c r="N41">
-        <v>-32.6856990666667</v>
+        <v>-37.9759306666667</v>
       </c>
       <c r="O41">
-        <v>-7.517710785333342</v>
+        <v>-8.73446405333334</v>
       </c>
       <c r="P41">
-        <v>-25.16798828133336</v>
+        <v>-29.24146661333336</v>
       </c>
       <c r="Q41">
-        <v>63.03201171866665</v>
+        <v>58.95853338666664</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08944633140005503</v>
+        <v>0.09017377025672263</v>
       </c>
       <c r="T41">
-        <v>0.6751948655620842</v>
+        <v>0.6864481133214523</v>
       </c>
       <c r="U41">
         <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.1935626888228207</v>
+        <v>0.1887236216022502</v>
       </c>
       <c r="W41">
-        <v>0.1183849972808099</v>
+        <v>0.1190953723487897</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.8415769079253074</v>
+        <v>0.8205374852271747</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4817,22 +4817,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1017424110935495</v>
+        <v>0.1027524110935494</v>
       </c>
       <c r="C42">
-        <v>670.0248997513054</v>
+        <v>602.0327302720118</v>
       </c>
       <c r="D42">
-        <v>1801.904899751305</v>
+        <v>1769.949730272012</v>
       </c>
       <c r="E42">
-        <v>-79.22000000000003</v>
+        <v>-43.18299999999999</v>
       </c>
       <c r="F42">
-        <v>1441.48</v>
+        <v>1477.517</v>
       </c>
       <c r="G42">
         <v>309.6</v>
@@ -4853,37 +4853,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M42">
-        <v>211.609264</v>
+        <v>216.8994956</v>
       </c>
       <c r="N42">
-        <v>-37.9759306666667</v>
+        <v>-43.2661622666667</v>
       </c>
       <c r="O42">
-        <v>-8.73446405333334</v>
+        <v>-9.95121732133334</v>
       </c>
       <c r="P42">
-        <v>-29.24146661333336</v>
+        <v>-33.31494494533336</v>
       </c>
       <c r="Q42">
-        <v>58.95853338666664</v>
+        <v>54.88505505466664</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09017377025672263</v>
+        <v>0.09092586805768402</v>
       </c>
       <c r="T42">
-        <v>0.6864481133214523</v>
+        <v>0.6980828271065616</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.1887236216022502</v>
+        <v>0.1841206064412197</v>
       </c>
       <c r="W42">
-        <v>0.1190953723487897</v>
+        <v>0.1197710949744289</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8205374852271747</v>
+        <v>0.8005243758313899</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4899,22 +4899,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1027524110935494</v>
+        <v>0.12702704232708</v>
       </c>
       <c r="C43">
-        <v>602.0327302720118</v>
+        <v>37.04778666436823</v>
       </c>
       <c r="D43">
-        <v>1769.949730272012</v>
+        <v>1241.001786664368</v>
       </c>
       <c r="E43">
-        <v>-43.18299999999999</v>
+        <v>-7.145999999999958</v>
       </c>
       <c r="F43">
-        <v>1477.517</v>
+        <v>1513.554</v>
       </c>
       <c r="G43">
         <v>309.6</v>
@@ -4935,45 +4935,45 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M43">
-        <v>216.8994956</v>
+        <v>303.9216432</v>
       </c>
       <c r="N43">
-        <v>-43.2661622666667</v>
+        <v>-130.2883098666667</v>
       </c>
       <c r="O43">
-        <v>-9.95121732133334</v>
+        <v>-29.96631126933334</v>
       </c>
       <c r="P43">
-        <v>-33.31494494533336</v>
+        <v>-100.3219985973333</v>
       </c>
       <c r="Q43">
-        <v>54.88505505466664</v>
+        <v>-12.12199859733333</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09092586805768402</v>
+        <v>0.09271188515097259</v>
       </c>
       <c r="T43">
-        <v>0.6980828271065616</v>
+        <v>0.7257119435182341</v>
       </c>
       <c r="U43">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1841206064412197</v>
+        <v>0.1314011935648375</v>
       </c>
       <c r="W43">
-        <v>0.1197710949744289</v>
+        <v>0.1744146403321806</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y43">
-        <v>0.8005243758313899</v>
+        <v>0.5713095372384237</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4981,22 +4981,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.12702704232708</v>
+        <v>0.12857704232708</v>
       </c>
       <c r="C44">
-        <v>37.04778666436891</v>
+        <v>-22.22697002823179</v>
       </c>
       <c r="D44">
-        <v>1241.001786664369</v>
+        <v>1217.764029971768</v>
       </c>
       <c r="E44">
-        <v>-7.146000000000186</v>
+        <v>28.89099999999985</v>
       </c>
       <c r="F44">
-        <v>1513.554</v>
+        <v>1549.591</v>
       </c>
       <c r="G44">
         <v>309.6</v>
@@ -5017,37 +5017,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M44">
-        <v>303.9216432</v>
+        <v>311.1578728</v>
       </c>
       <c r="N44">
-        <v>-130.2883098666667</v>
+        <v>-137.5245394666667</v>
       </c>
       <c r="O44">
-        <v>-29.96631126933334</v>
+        <v>-31.63064407733334</v>
       </c>
       <c r="P44">
-        <v>-100.3219985973333</v>
+        <v>-105.8938953893334</v>
       </c>
       <c r="Q44">
-        <v>-12.12199859733333</v>
+        <v>-17.69389538933335</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09271188515097259</v>
+        <v>0.09353490067993701</v>
       </c>
       <c r="T44">
-        <v>0.7257119435182341</v>
+        <v>0.7384437320010101</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.1314011935648375</v>
+        <v>0.1283453518540273</v>
       </c>
       <c r="W44">
-        <v>0.1744146403321806</v>
+        <v>0.1750282533477113</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5713095372384237</v>
+        <v>0.5580232689305533</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5063,22 +5063,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.12857704232708</v>
+        <v>0.13012704232708</v>
       </c>
       <c r="C45">
-        <v>-22.22697002823179</v>
+        <v>-80.6474687774828</v>
       </c>
       <c r="D45">
-        <v>1217.764029971768</v>
+        <v>1195.380531222517</v>
       </c>
       <c r="E45">
-        <v>28.89099999999985</v>
+        <v>64.92799999999988</v>
       </c>
       <c r="F45">
-        <v>1549.591</v>
+        <v>1585.628</v>
       </c>
       <c r="G45">
         <v>309.6</v>
@@ -5099,37 +5099,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M45">
-        <v>311.1578728</v>
+        <v>318.3941024</v>
       </c>
       <c r="N45">
-        <v>-137.5245394666667</v>
+        <v>-144.7607690666667</v>
       </c>
       <c r="O45">
-        <v>-31.63064407733334</v>
+        <v>-33.29497688533334</v>
       </c>
       <c r="P45">
-        <v>-105.8938953893334</v>
+        <v>-111.4657921813333</v>
       </c>
       <c r="Q45">
-        <v>-17.69389538933335</v>
+        <v>-23.26579218133334</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09353490067993701</v>
+        <v>0.09438730962065017</v>
       </c>
       <c r="T45">
-        <v>0.7384437320010101</v>
+        <v>0.7516302272153139</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1283453518540273</v>
+        <v>0.125428412039163</v>
       </c>
       <c r="W45">
-        <v>0.1750282533477113</v>
+        <v>0.1756139748625361</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5580232689305533</v>
+        <v>0.5453409219094044</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5145,22 +5145,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.13012704232708</v>
+        <v>0.13167704232708</v>
       </c>
       <c r="C46">
-        <v>-80.6474687774828</v>
+        <v>-138.2599652453046</v>
       </c>
       <c r="D46">
-        <v>1195.380531222517</v>
+        <v>1173.805034754695</v>
       </c>
       <c r="E46">
-        <v>64.92799999999988</v>
+        <v>100.9649999999999</v>
       </c>
       <c r="F46">
-        <v>1585.628</v>
+        <v>1621.665</v>
       </c>
       <c r="G46">
         <v>309.6</v>
@@ -5181,37 +5181,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M46">
-        <v>318.3941024</v>
+        <v>325.630332</v>
       </c>
       <c r="N46">
-        <v>-144.7607690666667</v>
+        <v>-151.9969986666667</v>
       </c>
       <c r="O46">
-        <v>-33.29497688533334</v>
+        <v>-34.95930969333334</v>
       </c>
       <c r="P46">
-        <v>-111.4657921813333</v>
+        <v>-117.0376889733333</v>
       </c>
       <c r="Q46">
-        <v>-23.26579218133334</v>
+        <v>-28.83768897333334</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09438730962065017</v>
+        <v>0.09527071525011654</v>
       </c>
       <c r="T46">
-        <v>0.7516302272153139</v>
+        <v>0.7652962313465013</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.125428412039163</v>
+        <v>0.1226411139938483</v>
       </c>
       <c r="W46">
-        <v>0.1756139748625361</v>
+        <v>0.1761736643100353</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5453409219094044</v>
+        <v>0.5332222347558622</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.13167704232708</v>
+        <v>0.13322704232708</v>
       </c>
       <c r="C47">
-        <v>-138.2599652453046</v>
+        <v>-195.1074348144691</v>
       </c>
       <c r="D47">
-        <v>1173.805034754695</v>
+        <v>1152.994565185531</v>
       </c>
       <c r="E47">
-        <v>100.9649999999999</v>
+        <v>137.002</v>
       </c>
       <c r="F47">
-        <v>1621.665</v>
+        <v>1657.702</v>
       </c>
       <c r="G47">
         <v>309.6</v>
@@ -5263,37 +5263,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M47">
-        <v>325.630332</v>
+        <v>332.8665616</v>
       </c>
       <c r="N47">
-        <v>-151.9969986666667</v>
+        <v>-159.2332282666667</v>
       </c>
       <c r="O47">
-        <v>-34.95930969333334</v>
+        <v>-36.62364250133334</v>
       </c>
       <c r="P47">
-        <v>-117.0376889733333</v>
+        <v>-122.6095857653333</v>
       </c>
       <c r="Q47">
-        <v>-28.83768897333334</v>
+        <v>-34.40958576533335</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09527071525011654</v>
+        <v>0.09618683960660018</v>
       </c>
       <c r="T47">
-        <v>0.7652962313465013</v>
+        <v>0.7794683837788441</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1226411139938483</v>
+        <v>0.119975002820069</v>
       </c>
       <c r="W47">
-        <v>0.1761736643100353</v>
+        <v>0.1767090194337302</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5332222347558622</v>
+        <v>0.5216304470437781</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5309,22 +5309,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.13322704232708</v>
+        <v>0.13477704232708</v>
       </c>
       <c r="C48">
-        <v>-195.1074348144691</v>
+        <v>-251.2298583045881</v>
       </c>
       <c r="D48">
-        <v>1152.994565185531</v>
+        <v>1132.909141695412</v>
       </c>
       <c r="E48">
-        <v>137.002</v>
+        <v>173.039</v>
       </c>
       <c r="F48">
-        <v>1657.702</v>
+        <v>1693.739</v>
       </c>
       <c r="G48">
         <v>309.6</v>
@@ -5345,37 +5345,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M48">
-        <v>332.8665616</v>
+        <v>340.1027912</v>
       </c>
       <c r="N48">
-        <v>-159.2332282666667</v>
+        <v>-166.4694578666667</v>
       </c>
       <c r="O48">
-        <v>-36.62364250133334</v>
+        <v>-38.28797530933334</v>
       </c>
       <c r="P48">
-        <v>-122.6095857653333</v>
+        <v>-128.1814825573333</v>
       </c>
       <c r="Q48">
-        <v>-34.40958576533335</v>
+        <v>-39.98148255733334</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09618683960660018</v>
+        <v>0.09713753469351717</v>
       </c>
       <c r="T48">
-        <v>0.7794683837788441</v>
+        <v>0.7941753344161807</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.119975002820069</v>
+        <v>0.1174223431855994</v>
       </c>
       <c r="W48">
-        <v>0.1767090194337302</v>
+        <v>0.1772215934883316</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5216304470437781</v>
+        <v>0.5105319268939106</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5391,22 +5391,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.13477704232708</v>
+        <v>0.1533629480913717</v>
       </c>
       <c r="C49">
-        <v>-251.2298583045881</v>
+        <v>-483.0233238968938</v>
       </c>
       <c r="D49">
-        <v>1132.909141695412</v>
+        <v>937.1526761031063</v>
       </c>
       <c r="E49">
-        <v>173.039</v>
+        <v>209.076</v>
       </c>
       <c r="F49">
-        <v>1693.739</v>
+        <v>1729.776</v>
       </c>
       <c r="G49">
         <v>309.6</v>
@@ -5427,45 +5427,45 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M49">
-        <v>340.1027912</v>
+        <v>407.8811808</v>
       </c>
       <c r="N49">
-        <v>-166.4694578666667</v>
+        <v>-234.2478474666667</v>
       </c>
       <c r="O49">
-        <v>-38.28797530933334</v>
+        <v>-53.87700491733334</v>
       </c>
       <c r="P49">
-        <v>-128.1814825573333</v>
+        <v>-180.3708425493334</v>
       </c>
       <c r="Q49">
-        <v>-39.98148255733334</v>
+        <v>-92.17084254933336</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09713753469351717</v>
+        <v>0.09857845990741512</v>
       </c>
       <c r="T49">
-        <v>0.7941753344161807</v>
+        <v>0.8164659892060496</v>
       </c>
       <c r="U49">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.1174223431855994</v>
+        <v>0.09791004965793867</v>
       </c>
       <c r="W49">
-        <v>0.1772215934883316</v>
+        <v>0.2127128102906581</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y49">
-        <v>0.5105319268939106</v>
+        <v>0.4256958680779942</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5473,22 +5473,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1533629480913717</v>
+        <v>0.1552629480913717</v>
       </c>
       <c r="C50">
-        <v>-483.0233238968931</v>
+        <v>-535.3269247480746</v>
       </c>
       <c r="D50">
-        <v>937.1526761031066</v>
+        <v>920.8860752519254</v>
       </c>
       <c r="E50">
-        <v>209.0759999999998</v>
+        <v>245.1129999999998</v>
       </c>
       <c r="F50">
-        <v>1729.776</v>
+        <v>1765.813</v>
       </c>
       <c r="G50">
         <v>309.6</v>
@@ -5509,37 +5509,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M50">
-        <v>407.8811808</v>
+        <v>416.3787054</v>
       </c>
       <c r="N50">
-        <v>-234.2478474666667</v>
+        <v>-242.7453720666667</v>
       </c>
       <c r="O50">
-        <v>-53.87700491733333</v>
+        <v>-55.83143557533334</v>
       </c>
       <c r="P50">
-        <v>-180.3708425493333</v>
+        <v>-186.9139364913333</v>
       </c>
       <c r="Q50">
-        <v>-92.17084254933333</v>
+        <v>-98.71393649133334</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09857845990741512</v>
+        <v>0.09961333167030562</v>
       </c>
       <c r="T50">
-        <v>0.8164659892060495</v>
+        <v>0.8324751262493055</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.09791004965793869</v>
+        <v>0.09591188537920524</v>
       </c>
       <c r="W50">
-        <v>0.2127128102906581</v>
+        <v>0.2131839774275834</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4256958680779943</v>
+        <v>0.4170081973008923</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5555,22 +5555,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1552629480913717</v>
+        <v>0.1571629480913717</v>
       </c>
       <c r="C51">
-        <v>-535.3269247480746</v>
+        <v>-587.0754659111469</v>
       </c>
       <c r="D51">
-        <v>920.8860752519254</v>
+        <v>905.174534088853</v>
       </c>
       <c r="E51">
-        <v>245.1129999999998</v>
+        <v>281.1499999999999</v>
       </c>
       <c r="F51">
-        <v>1765.813</v>
+        <v>1801.85</v>
       </c>
       <c r="G51">
         <v>309.6</v>
@@ -5591,37 +5591,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M51">
-        <v>416.3787054</v>
+        <v>424.87623</v>
       </c>
       <c r="N51">
-        <v>-242.7453720666667</v>
+        <v>-251.2428966666667</v>
       </c>
       <c r="O51">
-        <v>-55.83143557533334</v>
+        <v>-57.78586623333334</v>
       </c>
       <c r="P51">
-        <v>-186.9139364913333</v>
+        <v>-193.4570304333334</v>
       </c>
       <c r="Q51">
-        <v>-98.71393649133334</v>
+        <v>-105.2570304333334</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09961333167030562</v>
+        <v>0.1006895983037117</v>
       </c>
       <c r="T51">
-        <v>0.8324751262493055</v>
+        <v>0.8491246287742916</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.09591188537920524</v>
+        <v>0.09399364767162113</v>
       </c>
       <c r="W51">
-        <v>0.2131839774275834</v>
+        <v>0.2136362978790317</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.4170081973008923</v>
+        <v>0.4086680333548744</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5637,22 +5637,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1571629480913717</v>
+        <v>0.1590629480913717</v>
       </c>
       <c r="C52">
-        <v>-587.0754659111469</v>
+        <v>-638.2968809714132</v>
       </c>
       <c r="D52">
-        <v>905.174534088853</v>
+        <v>889.9901190285866</v>
       </c>
       <c r="E52">
-        <v>281.1499999999999</v>
+        <v>317.1869999999999</v>
       </c>
       <c r="F52">
-        <v>1801.85</v>
+        <v>1837.887</v>
       </c>
       <c r="G52">
         <v>309.6</v>
@@ -5673,37 +5673,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M52">
-        <v>424.87623</v>
+        <v>433.3737546</v>
       </c>
       <c r="N52">
-        <v>-251.2428966666667</v>
+        <v>-259.7404212666667</v>
       </c>
       <c r="O52">
-        <v>-57.78586623333334</v>
+        <v>-59.74029689133334</v>
       </c>
       <c r="P52">
-        <v>-193.4570304333334</v>
+        <v>-200.0001243753333</v>
       </c>
       <c r="Q52">
-        <v>-105.2570304333334</v>
+        <v>-111.8001243753333</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1006895983037117</v>
+        <v>0.1018097941874609</v>
       </c>
       <c r="T52">
-        <v>0.8491246287742916</v>
+        <v>0.8664537028309098</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.09399364767162113</v>
+        <v>0.09215063497217758</v>
       </c>
       <c r="W52">
-        <v>0.2136362978790317</v>
+        <v>0.2140708802735605</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.4086680333548744</v>
+        <v>0.4006549346616417</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5719,22 +5719,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1590629480913717</v>
+        <v>0.1609629480913717</v>
       </c>
       <c r="C53">
-        <v>-638.2968809714132</v>
+        <v>-689.0172600805752</v>
       </c>
       <c r="D53">
-        <v>889.9901190285866</v>
+        <v>875.3067399194248</v>
       </c>
       <c r="E53">
-        <v>317.1869999999999</v>
+        <v>353.2239999999999</v>
       </c>
       <c r="F53">
-        <v>1837.887</v>
+        <v>1873.924</v>
       </c>
       <c r="G53">
         <v>309.6</v>
@@ -5755,37 +5755,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M53">
-        <v>433.3737546</v>
+        <v>441.8712792</v>
       </c>
       <c r="N53">
-        <v>-259.7404212666667</v>
+        <v>-268.2379458666667</v>
       </c>
       <c r="O53">
-        <v>-59.74029689133334</v>
+        <v>-61.69472754933334</v>
       </c>
       <c r="P53">
-        <v>-200.0001243753333</v>
+        <v>-206.5432183173334</v>
       </c>
       <c r="Q53">
-        <v>-111.8001243753333</v>
+        <v>-118.3432183173334</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1018097941874609</v>
+        <v>0.1029766648996997</v>
       </c>
       <c r="T53">
-        <v>0.8664537028309098</v>
+        <v>0.8845048216398871</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.09215063497217758</v>
+        <v>0.09037850737655878</v>
       </c>
       <c r="W53">
-        <v>0.2140708802735605</v>
+        <v>0.2144887479606074</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.4006549346616417</v>
+        <v>0.3929500320719947</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5801,22 +5801,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1609629480913717</v>
+        <v>0.1628629480913718</v>
       </c>
       <c r="C54">
-        <v>-689.0172600805752</v>
+        <v>-739.2609995567486</v>
       </c>
       <c r="D54">
-        <v>875.3067399194248</v>
+        <v>861.1000004432514</v>
       </c>
       <c r="E54">
-        <v>353.2239999999999</v>
+        <v>389.261</v>
       </c>
       <c r="F54">
-        <v>1873.924</v>
+        <v>1909.961</v>
       </c>
       <c r="G54">
         <v>309.6</v>
@@ -5837,37 +5837,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M54">
-        <v>441.8712792</v>
+        <v>450.3688038</v>
       </c>
       <c r="N54">
-        <v>-268.2379458666667</v>
+        <v>-276.7354704666667</v>
       </c>
       <c r="O54">
-        <v>-61.69472754933334</v>
+        <v>-63.64915820733334</v>
       </c>
       <c r="P54">
-        <v>-206.5432183173334</v>
+        <v>-213.0863122593333</v>
       </c>
       <c r="Q54">
-        <v>-118.3432183173334</v>
+        <v>-124.8863122593333</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1029766648996997</v>
+        <v>0.1041931896847997</v>
       </c>
       <c r="T54">
-        <v>0.8845048216398871</v>
+        <v>0.9033240731641401</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.09037850737655878</v>
+        <v>0.0886732525203973</v>
       </c>
       <c r="W54">
-        <v>0.2144887479606074</v>
+        <v>0.2148908470556903</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3929500320719947</v>
+        <v>0.3855358805234664</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5883,22 +5883,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1628629480913718</v>
+        <v>0.1647629480913717</v>
       </c>
       <c r="C55">
-        <v>-739.2609995567486</v>
+        <v>-789.0509371485905</v>
       </c>
       <c r="D55">
-        <v>861.1000004432514</v>
+        <v>847.3470628514096</v>
       </c>
       <c r="E55">
-        <v>389.261</v>
+        <v>425.298</v>
       </c>
       <c r="F55">
-        <v>1909.961</v>
+        <v>1945.998</v>
       </c>
       <c r="G55">
         <v>309.6</v>
@@ -5919,37 +5919,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M55">
-        <v>450.3688038</v>
+        <v>458.8663284</v>
       </c>
       <c r="N55">
-        <v>-276.7354704666667</v>
+        <v>-285.2329950666667</v>
       </c>
       <c r="O55">
-        <v>-63.64915820733334</v>
+        <v>-65.60358886533335</v>
       </c>
       <c r="P55">
-        <v>-213.0863122593333</v>
+        <v>-219.6294062013334</v>
       </c>
       <c r="Q55">
-        <v>-124.8863122593333</v>
+        <v>-131.4294062013334</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1041931896847997</v>
+        <v>0.1054626068518606</v>
       </c>
       <c r="T55">
-        <v>0.9033240731641401</v>
+        <v>0.9229615530155343</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.0886732525203973</v>
+        <v>0.08703115525150104</v>
       </c>
       <c r="W55">
-        <v>0.2148908470556903</v>
+        <v>0.2152780535916961</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3855358805234664</v>
+        <v>0.3783963271804394</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5965,22 +5965,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1647629480913717</v>
+        <v>0.1666629480913717</v>
       </c>
       <c r="C56">
-        <v>-789.0509371485905</v>
+        <v>-838.4084745410803</v>
       </c>
       <c r="D56">
-        <v>847.3470628514096</v>
+        <v>834.0265254589197</v>
       </c>
       <c r="E56">
-        <v>425.298</v>
+        <v>461.335</v>
       </c>
       <c r="F56">
-        <v>1945.998</v>
+        <v>1982.035</v>
       </c>
       <c r="G56">
         <v>309.6</v>
@@ -6001,37 +6001,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M56">
-        <v>458.8663284</v>
+        <v>467.3638530000001</v>
       </c>
       <c r="N56">
-        <v>-285.2329950666667</v>
+        <v>-293.7305196666667</v>
       </c>
       <c r="O56">
-        <v>-65.60358886533335</v>
+        <v>-67.55801952333336</v>
       </c>
       <c r="P56">
-        <v>-219.6294062013334</v>
+        <v>-226.1725001433334</v>
       </c>
       <c r="Q56">
-        <v>-131.4294062013334</v>
+        <v>-137.9725001433334</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1054626068518606</v>
+        <v>0.1067884425596797</v>
       </c>
       <c r="T56">
-        <v>0.9229615530155343</v>
+        <v>0.943471809749213</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.08703115525150104</v>
+        <v>0.08544877061056466</v>
       </c>
       <c r="W56">
-        <v>0.2152780535916961</v>
+        <v>0.2156511798900289</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3783963271804394</v>
+        <v>0.3715163939589767</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6047,22 +6047,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1666629480913717</v>
+        <v>0.1685629480913717</v>
       </c>
       <c r="C57">
-        <v>-838.4084745410803</v>
+        <v>-887.353688485181</v>
       </c>
       <c r="D57">
-        <v>834.0265254589197</v>
+        <v>821.1183115148191</v>
       </c>
       <c r="E57">
-        <v>461.335</v>
+        <v>497.3720000000001</v>
       </c>
       <c r="F57">
-        <v>1982.035</v>
+        <v>2018.072</v>
       </c>
       <c r="G57">
         <v>309.6</v>
@@ -6083,37 +6083,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M57">
-        <v>467.3638530000001</v>
+        <v>475.8613776</v>
       </c>
       <c r="N57">
-        <v>-293.7305196666667</v>
+        <v>-302.2280442666667</v>
       </c>
       <c r="O57">
-        <v>-67.55801952333336</v>
+        <v>-69.51245018133335</v>
       </c>
       <c r="P57">
-        <v>-226.1725001433334</v>
+        <v>-232.7155940853334</v>
       </c>
       <c r="Q57">
-        <v>-137.9725001433334</v>
+        <v>-144.5155940853334</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1067884425596797</v>
+        <v>0.1081745435269451</v>
       </c>
       <c r="T57">
-        <v>0.943471809749213</v>
+        <v>0.9649143508798769</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.08544877061056466</v>
+        <v>0.08392289970680458</v>
       </c>
       <c r="W57">
-        <v>0.2156511798900289</v>
+        <v>0.2160109802491355</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3715163939589767</v>
+        <v>0.3648821726382808</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6129,22 +6129,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1685629480913717</v>
+        <v>0.1704629480913717</v>
       </c>
       <c r="C58">
-        <v>-887.353688485181</v>
+        <v>-935.9054317650739</v>
       </c>
       <c r="D58">
-        <v>821.1183115148191</v>
+        <v>808.603568234926</v>
       </c>
       <c r="E58">
-        <v>497.3720000000001</v>
+        <v>533.4089999999999</v>
       </c>
       <c r="F58">
-        <v>2018.072</v>
+        <v>2054.109</v>
       </c>
       <c r="G58">
         <v>309.6</v>
@@ -6165,37 +6165,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M58">
-        <v>475.8613776</v>
+        <v>484.3589022</v>
       </c>
       <c r="N58">
-        <v>-302.2280442666667</v>
+        <v>-310.7255688666667</v>
       </c>
       <c r="O58">
-        <v>-69.51245018133335</v>
+        <v>-71.46688083933334</v>
       </c>
       <c r="P58">
-        <v>-232.7155940853334</v>
+        <v>-239.2586880273333</v>
       </c>
       <c r="Q58">
-        <v>-144.5155940853334</v>
+        <v>-151.0586880273333</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1081745435269451</v>
+        <v>0.1096251143066415</v>
       </c>
       <c r="T58">
-        <v>0.9649143508798769</v>
+        <v>0.9873542195049904</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.08392289970680458</v>
+        <v>0.08245056813300099</v>
       </c>
       <c r="W58">
-        <v>0.2160109802491355</v>
+        <v>0.2163581560342384</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3648821726382808</v>
+        <v>0.3584807310130478</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6211,22 +6211,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1704629480913717</v>
+        <v>0.1723629480913718</v>
       </c>
       <c r="C59">
-        <v>-935.9054317650739</v>
+        <v>-984.081425070897</v>
       </c>
       <c r="D59">
-        <v>808.603568234926</v>
+        <v>796.4645749291032</v>
       </c>
       <c r="E59">
-        <v>533.4089999999999</v>
+        <v>569.4460000000001</v>
       </c>
       <c r="F59">
-        <v>2054.109</v>
+        <v>2090.146</v>
       </c>
       <c r="G59">
         <v>309.6</v>
@@ -6247,37 +6247,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M59">
-        <v>484.3589022</v>
+        <v>492.8564268000001</v>
       </c>
       <c r="N59">
-        <v>-310.7255688666667</v>
+        <v>-319.2230934666667</v>
       </c>
       <c r="O59">
-        <v>-71.46688083933334</v>
+        <v>-73.42131149733335</v>
       </c>
       <c r="P59">
-        <v>-239.2586880273333</v>
+        <v>-245.8017819693334</v>
       </c>
       <c r="Q59">
-        <v>-151.0586880273333</v>
+        <v>-157.6017819693334</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1096251143066415</v>
+        <v>0.1111447598853711</v>
       </c>
       <c r="T59">
-        <v>0.9873542195049904</v>
+        <v>1.010862653302728</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.08245056813300099</v>
+        <v>0.08102900661346649</v>
       </c>
       <c r="W59">
-        <v>0.2163581560342384</v>
+        <v>0.2166933602405446</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3584807310130478</v>
+        <v>0.3523000287542021</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1723629480913717</v>
+        <v>0.1742629480913717</v>
       </c>
       <c r="C60">
-        <v>-984.0814250708966</v>
+        <v>-1031.898340718551</v>
       </c>
       <c r="D60">
-        <v>796.4645749291032</v>
+        <v>784.6846592814494</v>
       </c>
       <c r="E60">
-        <v>569.4459999999997</v>
+        <v>605.4829999999999</v>
       </c>
       <c r="F60">
-        <v>2090.146</v>
+        <v>2126.183</v>
       </c>
       <c r="G60">
         <v>309.6</v>
@@ -6329,37 +6329,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M60">
-        <v>492.8564268</v>
+        <v>501.3539514</v>
       </c>
       <c r="N60">
-        <v>-319.2230934666666</v>
+        <v>-327.7206180666667</v>
       </c>
       <c r="O60">
-        <v>-73.42131149733332</v>
+        <v>-75.37574215533334</v>
       </c>
       <c r="P60">
-        <v>-245.8017819693333</v>
+        <v>-252.3448759113334</v>
       </c>
       <c r="Q60">
-        <v>-157.6017819693333</v>
+        <v>-164.1448759113334</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1111447598853711</v>
+        <v>0.1127385345167216</v>
       </c>
       <c r="T60">
-        <v>1.010862653302728</v>
+        <v>1.035517839968648</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.0810290066134665</v>
+        <v>0.0796556336200179</v>
       </c>
       <c r="W60">
-        <v>0.2166933602405446</v>
+        <v>0.2170172015923998</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3523000287542022</v>
+        <v>0.3463288418261649</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6375,22 +6375,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1742629480913717</v>
+        <v>0.1761629480913717</v>
       </c>
       <c r="C61">
-        <v>-1031.898340718551</v>
+        <v>-1079.371879048366</v>
       </c>
       <c r="D61">
-        <v>784.6846592814494</v>
+        <v>773.2481209516337</v>
       </c>
       <c r="E61">
-        <v>605.4829999999999</v>
+        <v>641.5199999999998</v>
       </c>
       <c r="F61">
-        <v>2126.183</v>
+        <v>2162.22</v>
       </c>
       <c r="G61">
         <v>309.6</v>
@@ -6411,37 +6411,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M61">
-        <v>501.3539514</v>
+        <v>509.851476</v>
       </c>
       <c r="N61">
-        <v>-327.7206180666667</v>
+        <v>-336.2181426666667</v>
       </c>
       <c r="O61">
-        <v>-75.37574215533334</v>
+        <v>-77.33017281333333</v>
       </c>
       <c r="P61">
-        <v>-252.3448759113334</v>
+        <v>-258.8879698533333</v>
       </c>
       <c r="Q61">
-        <v>-164.1448759113334</v>
+        <v>-170.6879698533334</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1127385345167216</v>
+        <v>0.1144119978796397</v>
       </c>
       <c r="T61">
-        <v>1.035517839968648</v>
+        <v>1.061405785967865</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.0796556336200179</v>
+        <v>0.07832803972635094</v>
       </c>
       <c r="W61">
-        <v>0.2170172015923998</v>
+        <v>0.2173302482325264</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3463288418261649</v>
+        <v>0.3405566944623954</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6457,22 +6457,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1761629480913717</v>
+        <v>0.1780629480913717</v>
       </c>
       <c r="C62">
-        <v>-1079.371879048366</v>
+        <v>-1126.516838238821</v>
       </c>
       <c r="D62">
-        <v>773.2481209516337</v>
+        <v>762.1401617611793</v>
       </c>
       <c r="E62">
-        <v>641.5199999999998</v>
+        <v>677.557</v>
       </c>
       <c r="F62">
-        <v>2162.22</v>
+        <v>2198.257</v>
       </c>
       <c r="G62">
         <v>309.6</v>
@@ -6493,37 +6493,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M62">
-        <v>509.851476</v>
+        <v>518.3490006000001</v>
       </c>
       <c r="N62">
-        <v>-336.2181426666667</v>
+        <v>-344.7156672666667</v>
       </c>
       <c r="O62">
-        <v>-77.33017281333333</v>
+        <v>-79.28460347133336</v>
       </c>
       <c r="P62">
-        <v>-258.8879698533333</v>
+        <v>-265.4310637953334</v>
       </c>
       <c r="Q62">
-        <v>-170.6879698533334</v>
+        <v>-177.2310637953334</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1144119978796397</v>
+        <v>0.1161712798765535</v>
       </c>
       <c r="T62">
-        <v>1.061405785967865</v>
+        <v>1.088621318941399</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.07832803972635094</v>
+        <v>0.0770439735013288</v>
       </c>
       <c r="W62">
-        <v>0.2173302482325264</v>
+        <v>0.2176330310483867</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3405566944623954</v>
+        <v>0.3349737978318643</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6539,22 +6539,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1780629480913717</v>
+        <v>0.1799629480913717</v>
       </c>
       <c r="C63">
-        <v>-1126.516838238821</v>
+        <v>-1173.347178188089</v>
       </c>
       <c r="D63">
-        <v>762.1401617611793</v>
+        <v>751.3468218119109</v>
       </c>
       <c r="E63">
-        <v>677.557</v>
+        <v>713.5939999999998</v>
       </c>
       <c r="F63">
-        <v>2198.257</v>
+        <v>2234.294</v>
       </c>
       <c r="G63">
         <v>309.6</v>
@@ -6575,37 +6575,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M63">
-        <v>518.3490006000001</v>
+        <v>526.8465252</v>
       </c>
       <c r="N63">
-        <v>-344.7156672666667</v>
+        <v>-353.2131918666666</v>
       </c>
       <c r="O63">
-        <v>-79.28460347133336</v>
+        <v>-81.23903412933333</v>
       </c>
       <c r="P63">
-        <v>-265.4310637953334</v>
+        <v>-271.9741577373333</v>
       </c>
       <c r="Q63">
-        <v>-177.2310637953334</v>
+        <v>-183.7741577373333</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1161712798765535</v>
+        <v>0.1180231556627786</v>
       </c>
       <c r="T63">
-        <v>1.088621318941399</v>
+        <v>1.117269248387226</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.0770439735013288</v>
+        <v>0.07580132876743641</v>
       </c>
       <c r="W63">
-        <v>0.2176330310483867</v>
+        <v>0.2179260466766385</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3349737978318643</v>
+        <v>0.3295709946410278</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6621,22 +6621,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1799629480913717</v>
+        <v>0.1818629480913717</v>
       </c>
       <c r="C64">
-        <v>-1173.347178188089</v>
+        <v>-1219.876079043301</v>
       </c>
       <c r="D64">
-        <v>751.3468218119109</v>
+        <v>740.8549209566983</v>
       </c>
       <c r="E64">
-        <v>713.5939999999998</v>
+        <v>749.6309999999996</v>
       </c>
       <c r="F64">
-        <v>2234.294</v>
+        <v>2270.331</v>
       </c>
       <c r="G64">
         <v>309.6</v>
@@ -6657,37 +6657,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M64">
-        <v>526.8465252</v>
+        <v>535.3440498</v>
       </c>
       <c r="N64">
-        <v>-353.2131918666666</v>
+        <v>-361.7107164666667</v>
       </c>
       <c r="O64">
-        <v>-81.23903412933333</v>
+        <v>-83.19346478733334</v>
       </c>
       <c r="P64">
-        <v>-271.9741577373333</v>
+        <v>-278.5172516793333</v>
       </c>
       <c r="Q64">
-        <v>-183.7741577373333</v>
+        <v>-190.3172516793333</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1180231556627786</v>
+        <v>0.1199751328428537</v>
       </c>
       <c r="T64">
-        <v>1.117269248387226</v>
+        <v>1.147465714559853</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.07580132876743641</v>
+        <v>0.07459813307271519</v>
       </c>
       <c r="W64">
-        <v>0.2179260466766385</v>
+        <v>0.2182097602214537</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3295709946410278</v>
+        <v>0.3243397090118052</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6703,22 +6703,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1818629480913717</v>
+        <v>0.1837629480913717</v>
       </c>
       <c r="C65">
-        <v>-1219.876079043301</v>
+        <v>-1266.115994893472</v>
       </c>
       <c r="D65">
-        <v>740.8549209566983</v>
+        <v>730.6520051065276</v>
       </c>
       <c r="E65">
-        <v>749.6309999999996</v>
+        <v>785.6679999999999</v>
       </c>
       <c r="F65">
-        <v>2270.331</v>
+        <v>2306.368</v>
       </c>
       <c r="G65">
         <v>309.6</v>
@@ -6739,37 +6739,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M65">
-        <v>535.3440498</v>
+        <v>543.8415744</v>
       </c>
       <c r="N65">
-        <v>-361.7107164666667</v>
+        <v>-370.2082410666667</v>
       </c>
       <c r="O65">
-        <v>-83.19346478733334</v>
+        <v>-85.14789544533335</v>
       </c>
       <c r="P65">
-        <v>-278.5172516793333</v>
+        <v>-285.0603456213333</v>
       </c>
       <c r="Q65">
-        <v>-190.3172516793333</v>
+        <v>-196.8603456213334</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1199751328428537</v>
+        <v>0.1220355531995996</v>
       </c>
       <c r="T65">
-        <v>1.147465714559853</v>
+        <v>1.179339762186516</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.07459813307271519</v>
+        <v>0.07343253724345401</v>
       </c>
       <c r="W65">
-        <v>0.2182097602214537</v>
+        <v>0.2184846077179936</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3243397090118052</v>
+        <v>0.3192719010584957</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6785,22 +6785,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1837629480913717</v>
+        <v>0.1856629480913717</v>
       </c>
       <c r="C66">
-        <v>-1266.115994893472</v>
+        <v>-1312.078703086006</v>
       </c>
       <c r="D66">
-        <v>730.6520051065276</v>
+        <v>720.7262969139942</v>
       </c>
       <c r="E66">
-        <v>785.6679999999999</v>
+        <v>821.7049999999997</v>
       </c>
       <c r="F66">
-        <v>2306.368</v>
+        <v>2342.405</v>
       </c>
       <c r="G66">
         <v>309.6</v>
@@ -6821,37 +6821,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M66">
-        <v>543.8415744</v>
+        <v>552.3390989999999</v>
       </c>
       <c r="N66">
-        <v>-370.2082410666667</v>
+        <v>-378.7057656666666</v>
       </c>
       <c r="O66">
-        <v>-85.14789544533335</v>
+        <v>-87.10232610333333</v>
       </c>
       <c r="P66">
-        <v>-285.0603456213333</v>
+        <v>-291.6034395633333</v>
       </c>
       <c r="Q66">
-        <v>-196.8603456213334</v>
+        <v>-203.4034395633333</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1220355531995996</v>
+        <v>0.1242137118624453</v>
       </c>
       <c r="T66">
-        <v>1.179339762186516</v>
+        <v>1.213035183963274</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.07343253724345401</v>
+        <v>0.07230280590124703</v>
       </c>
       <c r="W66">
-        <v>0.2184846077179936</v>
+        <v>0.218750998368486</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3192719010584957</v>
+        <v>0.3143600256575958</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6867,22 +6867,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1856629480913717</v>
+        <v>0.1875629480913718</v>
       </c>
       <c r="C67">
-        <v>-1312.078703086006</v>
+        <v>-1357.775349577372</v>
       </c>
       <c r="D67">
-        <v>720.7262969139942</v>
+        <v>711.0666504226276</v>
       </c>
       <c r="E67">
-        <v>821.7049999999997</v>
+        <v>857.742</v>
       </c>
       <c r="F67">
-        <v>2342.405</v>
+        <v>2378.442</v>
       </c>
       <c r="G67">
         <v>309.6</v>
@@ -6903,37 +6903,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M67">
-        <v>552.3390989999999</v>
+        <v>560.8366236000001</v>
       </c>
       <c r="N67">
-        <v>-378.7057656666666</v>
+        <v>-387.2032902666667</v>
       </c>
       <c r="O67">
-        <v>-87.10232610333333</v>
+        <v>-89.05675676133335</v>
       </c>
       <c r="P67">
-        <v>-291.6034395633333</v>
+        <v>-298.1465335053334</v>
       </c>
       <c r="Q67">
-        <v>-203.4034395633333</v>
+        <v>-209.9465335053334</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1242137118624453</v>
+        <v>0.1265199975054584</v>
       </c>
       <c r="T67">
-        <v>1.213035183963274</v>
+        <v>1.248712689373958</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.07230280590124703</v>
+        <v>0.07120730884213722</v>
       </c>
       <c r="W67">
-        <v>0.218750998368486</v>
+        <v>0.2190093165750241</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3143600256575958</v>
+        <v>0.3095969949658139</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6949,22 +6949,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1875629480913718</v>
+        <v>0.1894629480913718</v>
       </c>
       <c r="C68">
-        <v>-1357.775349577372</v>
+        <v>-1403.216490685097</v>
       </c>
       <c r="D68">
-        <v>711.0666504226276</v>
+        <v>701.6625093149029</v>
       </c>
       <c r="E68">
-        <v>857.742</v>
+        <v>893.7789999999998</v>
       </c>
       <c r="F68">
-        <v>2378.442</v>
+        <v>2414.479</v>
       </c>
       <c r="G68">
         <v>309.6</v>
@@ -6985,37 +6985,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M68">
-        <v>560.8366236000001</v>
+        <v>569.3341482</v>
       </c>
       <c r="N68">
-        <v>-387.2032902666667</v>
+        <v>-395.7008148666666</v>
       </c>
       <c r="O68">
-        <v>-89.05675676133335</v>
+        <v>-91.01118741933333</v>
       </c>
       <c r="P68">
-        <v>-298.1465335053334</v>
+        <v>-304.6896274473333</v>
       </c>
       <c r="Q68">
-        <v>-209.9465335053334</v>
+        <v>-216.4896274473333</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1265199975054584</v>
+        <v>0.1289660580359269</v>
       </c>
       <c r="T68">
-        <v>1.248712689373958</v>
+        <v>1.286552467839836</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.07120730884213722</v>
+        <v>0.07014451318777698</v>
       </c>
       <c r="W68">
-        <v>0.2190093165750241</v>
+        <v>0.2192599237903222</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3095969949658139</v>
+        <v>0.3049761442946824</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7031,22 +7031,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1894629480913718</v>
+        <v>0.1913629480913717</v>
       </c>
       <c r="C69">
-        <v>-1403.216490685097</v>
+        <v>-1448.412131569874</v>
       </c>
       <c r="D69">
-        <v>701.6625093149029</v>
+        <v>692.5038684301259</v>
       </c>
       <c r="E69">
-        <v>893.7789999999998</v>
+        <v>929.816</v>
       </c>
       <c r="F69">
-        <v>2414.479</v>
+        <v>2450.516</v>
       </c>
       <c r="G69">
         <v>309.6</v>
@@ -7067,37 +7067,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M69">
-        <v>569.3341482</v>
+        <v>577.8316728000001</v>
       </c>
       <c r="N69">
-        <v>-395.7008148666666</v>
+        <v>-404.1983394666668</v>
       </c>
       <c r="O69">
-        <v>-91.01118741933333</v>
+        <v>-92.96561807733336</v>
       </c>
       <c r="P69">
-        <v>-304.6896274473333</v>
+        <v>-311.2327213893334</v>
       </c>
       <c r="Q69">
-        <v>-216.4896274473333</v>
+        <v>-223.0327213893334</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1289660580359269</v>
+        <v>0.1315649973495496</v>
       </c>
       <c r="T69">
-        <v>1.286552467839836</v>
+        <v>1.326757232459831</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.07014451318777698</v>
+        <v>0.06911297622913318</v>
       </c>
       <c r="W69">
-        <v>0.2192599237903222</v>
+        <v>0.2195031602051704</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3049761442946824</v>
+        <v>0.3004912009962312</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7113,22 +7113,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1913629480913717</v>
+        <v>0.1932629480913717</v>
       </c>
       <c r="C70">
-        <v>-1448.412131569874</v>
+        <v>-1493.371761742722</v>
       </c>
       <c r="D70">
-        <v>692.5038684301259</v>
+        <v>683.5812382572776</v>
       </c>
       <c r="E70">
-        <v>929.816</v>
+        <v>965.8529999999998</v>
       </c>
       <c r="F70">
-        <v>2450.516</v>
+        <v>2486.553</v>
       </c>
       <c r="G70">
         <v>309.6</v>
@@ -7149,37 +7149,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M70">
-        <v>577.8316728000001</v>
+        <v>586.3291974</v>
       </c>
       <c r="N70">
-        <v>-404.1983394666668</v>
+        <v>-412.6958640666667</v>
       </c>
       <c r="O70">
-        <v>-92.96561807733336</v>
+        <v>-94.92004873533334</v>
       </c>
       <c r="P70">
-        <v>-311.2327213893334</v>
+        <v>-317.7758153313333</v>
       </c>
       <c r="Q70">
-        <v>-223.0327213893334</v>
+        <v>-229.5758153313333</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1315649973495496</v>
+        <v>0.134331610167277</v>
       </c>
       <c r="T70">
-        <v>1.326757232459831</v>
+        <v>1.369555852861761</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.06911297622913318</v>
+        <v>0.06811133889247908</v>
       </c>
       <c r="W70">
-        <v>0.2195031602051704</v>
+        <v>0.2197393462891534</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3004912009962312</v>
+        <v>0.2961362560542569</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7195,22 +7195,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1932629480913717</v>
+        <v>0.1951629480913717</v>
       </c>
       <c r="C71">
-        <v>-1493.371761742722</v>
+        <v>-1538.104387862089</v>
       </c>
       <c r="D71">
-        <v>683.5812382572776</v>
+        <v>674.8856121379116</v>
       </c>
       <c r="E71">
-        <v>965.8529999999998</v>
+        <v>1001.89</v>
       </c>
       <c r="F71">
-        <v>2486.553</v>
+        <v>2522.59</v>
       </c>
       <c r="G71">
         <v>309.6</v>
@@ -7231,37 +7231,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M71">
-        <v>586.3291974</v>
+        <v>594.826722</v>
       </c>
       <c r="N71">
-        <v>-412.6958640666667</v>
+        <v>-421.1933886666667</v>
       </c>
       <c r="O71">
-        <v>-94.92004873533334</v>
+        <v>-96.87447939333335</v>
       </c>
       <c r="P71">
-        <v>-317.7758153313333</v>
+        <v>-324.3189092733334</v>
       </c>
       <c r="Q71">
-        <v>-229.5758153313333</v>
+        <v>-236.1189092733334</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.134331610167277</v>
+        <v>0.1372826638395196</v>
       </c>
       <c r="T71">
-        <v>1.369555852861761</v>
+        <v>1.41520771462382</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.06811133889247908</v>
+        <v>0.06713831976544367</v>
       </c>
       <c r="W71">
-        <v>0.2197393462891534</v>
+        <v>0.2199687841993084</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2961362560542569</v>
+        <v>0.2919057381106246</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7277,22 +7277,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1951629480913717</v>
+        <v>0.1970629480913718</v>
       </c>
       <c r="C72">
-        <v>-1538.104387862089</v>
+        <v>-1582.618564059179</v>
       </c>
       <c r="D72">
-        <v>674.8856121379116</v>
+        <v>666.4084359408205</v>
       </c>
       <c r="E72">
-        <v>1001.89</v>
+        <v>1037.927</v>
       </c>
       <c r="F72">
-        <v>2522.59</v>
+        <v>2558.627</v>
       </c>
       <c r="G72">
         <v>309.6</v>
@@ -7313,37 +7313,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M72">
-        <v>594.826722</v>
+        <v>603.3242466</v>
       </c>
       <c r="N72">
-        <v>-421.1933886666667</v>
+        <v>-429.6909132666667</v>
       </c>
       <c r="O72">
-        <v>-96.87447939333335</v>
+        <v>-98.82891005133335</v>
       </c>
       <c r="P72">
-        <v>-324.3189092733334</v>
+        <v>-330.8620032153333</v>
       </c>
       <c r="Q72">
-        <v>-236.1189092733334</v>
+        <v>-242.6620032153334</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1372826638395196</v>
+        <v>0.1404372384546754</v>
       </c>
       <c r="T72">
-        <v>1.41520771462382</v>
+        <v>1.464007980645331</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.06713831976544367</v>
+        <v>0.0661927096279022</v>
       </c>
       <c r="W72">
-        <v>0.2199687841993084</v>
+        <v>0.2201917590697407</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2919057381106246</v>
+        <v>0.2877943896865313</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7359,22 +7359,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1970629480913717</v>
+        <v>0.1989629480913717</v>
       </c>
       <c r="C73">
-        <v>-1582.618564059179</v>
+        <v>-1626.922420006169</v>
       </c>
       <c r="D73">
-        <v>666.4084359408205</v>
+        <v>658.1415799938312</v>
       </c>
       <c r="E73">
-        <v>1037.927</v>
+        <v>1073.964</v>
       </c>
       <c r="F73">
-        <v>2558.627</v>
+        <v>2594.664</v>
       </c>
       <c r="G73">
         <v>309.6</v>
@@ -7395,37 +7395,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M73">
-        <v>603.3242466</v>
+        <v>611.8217711999999</v>
       </c>
       <c r="N73">
-        <v>-429.6909132666667</v>
+        <v>-438.1884378666666</v>
       </c>
       <c r="O73">
-        <v>-98.82891005133335</v>
+        <v>-100.7833407093333</v>
       </c>
       <c r="P73">
-        <v>-330.8620032153333</v>
+        <v>-337.4050971573333</v>
       </c>
       <c r="Q73">
-        <v>-242.6620032153334</v>
+        <v>-249.2050971573333</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1404372384546754</v>
+        <v>0.1438171398280566</v>
       </c>
       <c r="T73">
-        <v>1.46400798064533</v>
+        <v>1.516293979954092</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.0661927096279022</v>
+        <v>0.06527336643862579</v>
       </c>
       <c r="W73">
-        <v>0.2201917590697407</v>
+        <v>0.220408540193772</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2877943896865313</v>
+        <v>0.2837972453853296</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7441,22 +7441,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1989629480913717</v>
+        <v>0.2008629480913717</v>
       </c>
       <c r="C74">
-        <v>-1626.922420006169</v>
+        <v>-1671.023686920864</v>
       </c>
       <c r="D74">
-        <v>658.1415799938312</v>
+        <v>650.0773130791364</v>
       </c>
       <c r="E74">
-        <v>1073.964</v>
+        <v>1110.001</v>
       </c>
       <c r="F74">
-        <v>2594.664</v>
+        <v>2630.701</v>
       </c>
       <c r="G74">
         <v>309.6</v>
@@ -7477,37 +7477,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M74">
-        <v>611.8217711999999</v>
+        <v>620.3192958000001</v>
       </c>
       <c r="N74">
-        <v>-438.1884378666666</v>
+        <v>-446.6859624666668</v>
       </c>
       <c r="O74">
-        <v>-100.7833407093333</v>
+        <v>-102.7377713673334</v>
       </c>
       <c r="P74">
-        <v>-337.4050971573333</v>
+        <v>-343.9481910993334</v>
       </c>
       <c r="Q74">
-        <v>-249.2050971573333</v>
+        <v>-255.7481910993334</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1438171398280566</v>
+        <v>0.1474474042661328</v>
       </c>
       <c r="T74">
-        <v>1.516293979954092</v>
+        <v>1.572453016248688</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.06527336643862579</v>
+        <v>0.06437921073398707</v>
       </c>
       <c r="W74">
-        <v>0.220408540193772</v>
+        <v>0.2206193821089258</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2837972453853296</v>
+        <v>0.2799096118869003</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7523,22 +7523,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2008629480913717</v>
+        <v>0.2027629480913717</v>
       </c>
       <c r="C75">
-        <v>-1671.023686920864</v>
+        <v>-1714.929721682694</v>
       </c>
       <c r="D75">
-        <v>650.0773130791364</v>
+        <v>642.2082783173063</v>
       </c>
       <c r="E75">
-        <v>1110.001</v>
+        <v>1146.038</v>
       </c>
       <c r="F75">
-        <v>2630.701</v>
+        <v>2666.738</v>
       </c>
       <c r="G75">
         <v>309.6</v>
@@ -7559,37 +7559,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M75">
-        <v>620.3192958000001</v>
+        <v>628.8168204</v>
       </c>
       <c r="N75">
-        <v>-446.6859624666668</v>
+        <v>-455.1834870666667</v>
       </c>
       <c r="O75">
-        <v>-102.7377713673334</v>
+        <v>-104.6922020253333</v>
       </c>
       <c r="P75">
-        <v>-343.9481910993334</v>
+        <v>-350.4912850413333</v>
       </c>
       <c r="Q75">
-        <v>-255.7481910993334</v>
+        <v>-262.2912850413333</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1474474042661328</v>
+        <v>0.1513569198148302</v>
       </c>
       <c r="T75">
-        <v>1.572453016248688</v>
+        <v>1.632931978412099</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.06437921073398707</v>
+        <v>0.06350922139974401</v>
       </c>
       <c r="W75">
-        <v>0.2206193821089258</v>
+        <v>0.2208245255939404</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2799096118869003</v>
+        <v>0.2761270495641044</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7605,22 +7605,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2027629480913717</v>
+        <v>0.2046629480913717</v>
       </c>
       <c r="C76">
-        <v>-1714.929721682694</v>
+        <v>-1758.647529218136</v>
       </c>
       <c r="D76">
-        <v>642.2082783173063</v>
+        <v>634.5274707818633</v>
       </c>
       <c r="E76">
-        <v>1146.038</v>
+        <v>1182.075</v>
       </c>
       <c r="F76">
-        <v>2666.738</v>
+        <v>2702.775</v>
       </c>
       <c r="G76">
         <v>309.6</v>
@@ -7641,37 +7641,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M76">
-        <v>628.8168204</v>
+        <v>637.3143449999999</v>
       </c>
       <c r="N76">
-        <v>-455.1834870666667</v>
+        <v>-463.6810116666666</v>
       </c>
       <c r="O76">
-        <v>-104.6922020253333</v>
+        <v>-106.6466326833333</v>
       </c>
       <c r="P76">
-        <v>-350.4912850413333</v>
+        <v>-357.0343789833332</v>
       </c>
       <c r="Q76">
-        <v>-262.2912850413333</v>
+        <v>-268.8343789833332</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1513569198148302</v>
+        <v>0.1555791966074234</v>
       </c>
       <c r="T76">
-        <v>1.632931978412099</v>
+        <v>1.698249257548583</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.06350922139974401</v>
+        <v>0.06266243178108077</v>
       </c>
       <c r="W76">
-        <v>0.2208245255939404</v>
+        <v>0.2210241985860212</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2761270495641044</v>
+        <v>0.2724453555699163</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7687,22 +7687,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2046629480913717</v>
+        <v>0.2065629480913718</v>
       </c>
       <c r="C77">
-        <v>-1758.647529218136</v>
+        <v>-1802.183783298749</v>
       </c>
       <c r="D77">
-        <v>634.5274707818633</v>
+        <v>627.0282167012507</v>
       </c>
       <c r="E77">
-        <v>1182.075</v>
+        <v>1218.112</v>
       </c>
       <c r="F77">
-        <v>2702.775</v>
+        <v>2738.812</v>
       </c>
       <c r="G77">
         <v>309.6</v>
@@ -7723,37 +7723,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M77">
-        <v>637.3143449999999</v>
+        <v>645.8118696</v>
       </c>
       <c r="N77">
-        <v>-463.6810116666666</v>
+        <v>-472.1785362666667</v>
       </c>
       <c r="O77">
-        <v>-106.6466326833333</v>
+        <v>-108.6010633413333</v>
       </c>
       <c r="P77">
-        <v>-357.0343789833332</v>
+        <v>-363.5774729253334</v>
       </c>
       <c r="Q77">
-        <v>-268.8343789833332</v>
+        <v>-275.3774729253334</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1555791966074234</v>
+        <v>0.1601533297993994</v>
       </c>
       <c r="T77">
-        <v>1.698249257548583</v>
+        <v>1.769009643279774</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06266243178108077</v>
+        <v>0.06183792609975074</v>
       </c>
       <c r="W77">
-        <v>0.2210241985860212</v>
+        <v>0.2212186170256788</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2724453555699163</v>
+        <v>0.2688605482597859</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7769,22 +7769,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2065629480913718</v>
+        <v>0.2084629480913717</v>
       </c>
       <c r="C78">
-        <v>-1802.183783298749</v>
+        <v>-1845.544845881601</v>
       </c>
       <c r="D78">
-        <v>627.0282167012507</v>
+        <v>619.7041541183987</v>
       </c>
       <c r="E78">
-        <v>1218.112</v>
+        <v>1254.149</v>
       </c>
       <c r="F78">
-        <v>2738.812</v>
+        <v>2774.849</v>
       </c>
       <c r="G78">
         <v>309.6</v>
@@ -7805,37 +7805,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M78">
-        <v>645.8118696</v>
+        <v>654.3093941999999</v>
       </c>
       <c r="N78">
-        <v>-472.1785362666667</v>
+        <v>-480.6760608666666</v>
       </c>
       <c r="O78">
-        <v>-108.6010633413333</v>
+        <v>-110.5554939993333</v>
       </c>
       <c r="P78">
-        <v>-363.5774729253334</v>
+        <v>-370.1205668673333</v>
       </c>
       <c r="Q78">
-        <v>-275.3774729253334</v>
+        <v>-281.9205668673333</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1601533297993994</v>
+        <v>0.1651252137037211</v>
       </c>
       <c r="T78">
-        <v>1.769009643279774</v>
+        <v>1.845923106031069</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06183792609975074</v>
+        <v>0.06103483615040334</v>
       </c>
       <c r="W78">
-        <v>0.2212186170256788</v>
+        <v>0.2214079856357349</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2688605482597859</v>
+        <v>0.2653688528278406</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7851,22 +7851,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2084629480913717</v>
+        <v>0.2103629480913717</v>
       </c>
       <c r="C79">
-        <v>-1845.544845881601</v>
+        <v>-1888.736785109909</v>
       </c>
       <c r="D79">
-        <v>619.7041541183987</v>
+        <v>612.5492148900909</v>
       </c>
       <c r="E79">
-        <v>1254.149</v>
+        <v>1290.186</v>
       </c>
       <c r="F79">
-        <v>2774.849</v>
+        <v>2810.886</v>
       </c>
       <c r="G79">
         <v>309.6</v>
@@ -7887,37 +7887,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M79">
-        <v>654.3093941999999</v>
+        <v>662.8069188000001</v>
       </c>
       <c r="N79">
-        <v>-480.6760608666666</v>
+        <v>-489.1735854666667</v>
       </c>
       <c r="O79">
-        <v>-110.5554939993333</v>
+        <v>-112.5099246573334</v>
       </c>
       <c r="P79">
-        <v>-370.1205668673333</v>
+        <v>-376.6636608093334</v>
       </c>
       <c r="Q79">
-        <v>-281.9205668673333</v>
+        <v>-288.4636608093334</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1651252137037211</v>
+        <v>0.1705490870538903</v>
       </c>
       <c r="T79">
-        <v>1.845923106031069</v>
+        <v>1.929828701759754</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06103483615040334</v>
+        <v>0.06025233825103919</v>
       </c>
       <c r="W79">
-        <v>0.2214079856357349</v>
+        <v>0.221592498640405</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2653688528278406</v>
+        <v>0.2619666880479965</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7933,22 +7933,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2103629480913717</v>
+        <v>0.2122629480913718</v>
       </c>
       <c r="C80">
-        <v>-1888.736785109909</v>
+        <v>-1931.765392080923</v>
       </c>
       <c r="D80">
-        <v>612.5492148900909</v>
+        <v>605.5576079190769</v>
       </c>
       <c r="E80">
-        <v>1290.186</v>
+        <v>1326.223</v>
       </c>
       <c r="F80">
-        <v>2810.886</v>
+        <v>2846.923</v>
       </c>
       <c r="G80">
         <v>309.6</v>
@@ -7969,37 +7969,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M80">
-        <v>662.8069188000001</v>
+        <v>671.3044434</v>
       </c>
       <c r="N80">
-        <v>-489.1735854666667</v>
+        <v>-497.6711100666666</v>
       </c>
       <c r="O80">
-        <v>-112.5099246573334</v>
+        <v>-114.4643553153333</v>
       </c>
       <c r="P80">
-        <v>-376.6636608093334</v>
+        <v>-383.2067547513333</v>
       </c>
       <c r="Q80">
-        <v>-288.4636608093334</v>
+        <v>-295.0067547513333</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1705490870538903</v>
+        <v>0.1764895197707422</v>
       </c>
       <c r="T80">
-        <v>1.929828701759754</v>
+        <v>2.021725306605456</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06025233825103919</v>
+        <v>0.05948965042507667</v>
       </c>
       <c r="W80">
-        <v>0.221592498640405</v>
+        <v>0.2217723404297669</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2619666880479965</v>
+        <v>0.2586506540220724</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8015,22 +8015,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2122629480913718</v>
+        <v>0.2141629480913718</v>
       </c>
       <c r="C81">
-        <v>-1931.765392080923</v>
+        <v>-1974.636196478443</v>
       </c>
       <c r="D81">
-        <v>605.5576079190769</v>
+        <v>598.7238035215568</v>
       </c>
       <c r="E81">
-        <v>1326.223</v>
+        <v>1362.26</v>
       </c>
       <c r="F81">
-        <v>2846.923</v>
+        <v>2882.96</v>
       </c>
       <c r="G81">
         <v>309.6</v>
@@ -8051,37 +8051,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M81">
-        <v>671.3044434</v>
+        <v>679.801968</v>
       </c>
       <c r="N81">
-        <v>-497.6711100666666</v>
+        <v>-506.1686346666667</v>
       </c>
       <c r="O81">
-        <v>-114.4643553153333</v>
+        <v>-116.4187859733333</v>
       </c>
       <c r="P81">
-        <v>-383.2067547513333</v>
+        <v>-389.7498486933333</v>
       </c>
       <c r="Q81">
-        <v>-295.0067547513333</v>
+        <v>-301.5498486933333</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1764895197707422</v>
+        <v>0.1830239957592794</v>
       </c>
       <c r="T81">
-        <v>2.021725306605456</v>
+        <v>2.122811571935729</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05948965042507667</v>
+        <v>0.05874602979476322</v>
       </c>
       <c r="W81">
-        <v>0.2217723404297669</v>
+        <v>0.2219476861743949</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2586506540220724</v>
+        <v>0.2554175208467966</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8097,22 +8097,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2141629480913718</v>
+        <v>0.2160629480913717</v>
       </c>
       <c r="C82">
-        <v>-1974.636196478443</v>
+        <v>-2017.354481158657</v>
       </c>
       <c r="D82">
-        <v>598.7238035215568</v>
+        <v>592.0425188413432</v>
       </c>
       <c r="E82">
-        <v>1362.26</v>
+        <v>1398.297</v>
       </c>
       <c r="F82">
-        <v>2882.96</v>
+        <v>2918.997</v>
       </c>
       <c r="G82">
         <v>309.6</v>
@@ -8133,37 +8133,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M82">
-        <v>679.801968</v>
+        <v>688.2994926</v>
       </c>
       <c r="N82">
-        <v>-506.1686346666667</v>
+        <v>-514.6661592666667</v>
       </c>
       <c r="O82">
-        <v>-116.4187859733333</v>
+        <v>-118.3732166313333</v>
       </c>
       <c r="P82">
-        <v>-389.7498486933333</v>
+        <v>-396.2929426353334</v>
       </c>
       <c r="Q82">
-        <v>-301.5498486933333</v>
+        <v>-308.0929426353334</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1830239957592794</v>
+        <v>0.1902463113255572</v>
       </c>
       <c r="T82">
-        <v>2.122811571935729</v>
+        <v>2.234538496774452</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05874602979476322</v>
+        <v>0.05802077016766737</v>
       </c>
       <c r="W82">
-        <v>0.2219476861743949</v>
+        <v>0.222118702394464</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2554175208467966</v>
+        <v>0.2522642181202929</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8179,22 +8179,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2160629480913717</v>
+        <v>0.2179629480913717</v>
       </c>
       <c r="C83">
-        <v>-2017.354481158657</v>
+        <v>-2059.925295770158</v>
       </c>
       <c r="D83">
-        <v>592.0425188413432</v>
+        <v>585.5087042298416</v>
       </c>
       <c r="E83">
-        <v>1398.297</v>
+        <v>1434.334</v>
       </c>
       <c r="F83">
-        <v>2918.997</v>
+        <v>2955.034</v>
       </c>
       <c r="G83">
         <v>309.6</v>
@@ -8215,37 +8215,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M83">
-        <v>688.2994926</v>
+        <v>696.7970172</v>
       </c>
       <c r="N83">
-        <v>-514.6661592666667</v>
+        <v>-523.1636838666667</v>
       </c>
       <c r="O83">
-        <v>-118.3732166313333</v>
+        <v>-120.3276472893333</v>
       </c>
       <c r="P83">
-        <v>-396.2929426353334</v>
+        <v>-402.8360365773333</v>
       </c>
       <c r="Q83">
-        <v>-308.0929426353334</v>
+        <v>-314.6360365773334</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1902463113255572</v>
+        <v>0.1982711063991993</v>
       </c>
       <c r="T83">
-        <v>2.234538496774452</v>
+        <v>2.358679524373033</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05802077016766737</v>
+        <v>0.05731319979976898</v>
       </c>
       <c r="W83">
-        <v>0.222118702394464</v>
+        <v>0.2222855474872145</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2522642181202929</v>
+        <v>0.2491878252163868</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8261,22 +8261,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2179629480913717</v>
+        <v>0.2198629480913718</v>
       </c>
       <c r="C84">
-        <v>-2059.925295770158</v>
+        <v>-2102.35346948194</v>
       </c>
       <c r="D84">
-        <v>585.5087042298416</v>
+        <v>579.1175305180601</v>
       </c>
       <c r="E84">
-        <v>1434.334</v>
+        <v>1470.371</v>
       </c>
       <c r="F84">
-        <v>2955.034</v>
+        <v>2991.071</v>
       </c>
       <c r="G84">
         <v>309.6</v>
@@ -8297,37 +8297,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M84">
-        <v>696.7970172</v>
+        <v>705.2945418</v>
       </c>
       <c r="N84">
-        <v>-523.1636838666667</v>
+        <v>-531.6612084666667</v>
       </c>
       <c r="O84">
-        <v>-120.3276472893333</v>
+        <v>-122.2820779473333</v>
       </c>
       <c r="P84">
-        <v>-402.8360365773333</v>
+        <v>-409.3791305193334</v>
       </c>
       <c r="Q84">
-        <v>-314.6360365773334</v>
+        <v>-321.1791305193334</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1982711063991993</v>
+        <v>0.2072399950109169</v>
       </c>
       <c r="T84">
-        <v>2.358679524373033</v>
+        <v>2.497425378747918</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05731319979976898</v>
+        <v>0.05662267932025369</v>
       </c>
       <c r="W84">
-        <v>0.2222855474872145</v>
+        <v>0.2224483722162842</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2491878252163868</v>
+        <v>0.2461855622619725</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8343,22 +8343,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2198629480913718</v>
+        <v>0.2217629480913718</v>
       </c>
       <c r="C85">
-        <v>-2102.35346948194</v>
+        <v>-2144.643622886786</v>
       </c>
       <c r="D85">
-        <v>579.1175305180601</v>
+        <v>572.8643771132143</v>
       </c>
       <c r="E85">
-        <v>1470.371</v>
+        <v>1506.408</v>
       </c>
       <c r="F85">
-        <v>2991.071</v>
+        <v>3027.108</v>
       </c>
       <c r="G85">
         <v>309.6</v>
@@ -8379,37 +8379,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M85">
-        <v>705.2945418</v>
+        <v>713.7920664000001</v>
       </c>
       <c r="N85">
-        <v>-531.6612084666667</v>
+        <v>-540.1587330666667</v>
       </c>
       <c r="O85">
-        <v>-122.2820779473333</v>
+        <v>-124.2365086053334</v>
       </c>
       <c r="P85">
-        <v>-409.3791305193334</v>
+        <v>-415.9222244613334</v>
       </c>
       <c r="Q85">
-        <v>-321.1791305193334</v>
+        <v>-327.7222244613334</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2072399950109169</v>
+        <v>0.2173299946990992</v>
       </c>
       <c r="T85">
-        <v>2.497425378747918</v>
+        <v>2.653514464919663</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05662267932025369</v>
+        <v>0.05594859980453638</v>
       </c>
       <c r="W85">
-        <v>0.2224483722162842</v>
+        <v>0.2226073201660903</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2461855622619725</v>
+        <v>0.2432547817588538</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8425,22 +8425,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2217629480913717</v>
+        <v>0.2236629480913717</v>
       </c>
       <c r="C86">
-        <v>-2144.643622886785</v>
+        <v>-2186.800179141728</v>
       </c>
       <c r="D86">
-        <v>572.8643771132143</v>
+        <v>566.7448208582716</v>
       </c>
       <c r="E86">
-        <v>1506.408</v>
+        <v>1542.445</v>
       </c>
       <c r="F86">
-        <v>3027.108</v>
+        <v>3063.145</v>
       </c>
       <c r="G86">
         <v>309.6</v>
@@ -8461,37 +8461,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M86">
-        <v>713.7920664</v>
+        <v>722.289591</v>
       </c>
       <c r="N86">
-        <v>-540.1587330666666</v>
+        <v>-548.6562576666666</v>
       </c>
       <c r="O86">
-        <v>-124.2365086053333</v>
+        <v>-126.1909392633333</v>
       </c>
       <c r="P86">
-        <v>-415.9222244613333</v>
+        <v>-422.4653184033333</v>
       </c>
       <c r="Q86">
-        <v>-327.7222244613333</v>
+        <v>-334.2653184033333</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2173299946990991</v>
+        <v>0.2287653276790391</v>
       </c>
       <c r="T86">
-        <v>2.653514464919661</v>
+        <v>2.830415429247639</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05594859980453639</v>
+        <v>0.05529038098330655</v>
       </c>
       <c r="W86">
-        <v>0.2226073201660903</v>
+        <v>0.2227625281641363</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2432547817588538</v>
+        <v>0.240392960796985</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8507,22 +8507,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2236629480913717</v>
+        <v>0.2255629480913717</v>
       </c>
       <c r="C87">
-        <v>-2186.800179141728</v>
+        <v>-2228.827374402007</v>
       </c>
       <c r="D87">
-        <v>566.7448208582716</v>
+        <v>560.7546255979926</v>
       </c>
       <c r="E87">
-        <v>1542.445</v>
+        <v>1578.482</v>
       </c>
       <c r="F87">
-        <v>3063.145</v>
+        <v>3099.182</v>
       </c>
       <c r="G87">
         <v>309.6</v>
@@ -8543,37 +8543,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M87">
-        <v>722.289591</v>
+        <v>730.7871156</v>
       </c>
       <c r="N87">
-        <v>-548.6562576666666</v>
+        <v>-557.1537822666667</v>
       </c>
       <c r="O87">
-        <v>-126.1909392633333</v>
+        <v>-128.1453699213333</v>
       </c>
       <c r="P87">
-        <v>-422.4653184033333</v>
+        <v>-429.0084123453333</v>
       </c>
       <c r="Q87">
-        <v>-334.2653184033333</v>
+        <v>-340.8084123453334</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2287653276790391</v>
+        <v>0.2418342796561133</v>
       </c>
       <c r="T87">
-        <v>2.830415429247639</v>
+        <v>3.032587959908184</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05529038098330655</v>
+        <v>0.05464746957652392</v>
       </c>
       <c r="W87">
-        <v>0.2227625281641363</v>
+        <v>0.2229141266738557</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.240392960796985</v>
+        <v>0.2375976938109735</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8589,22 +8589,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2255629480913717</v>
+        <v>0.2274629480913717</v>
       </c>
       <c r="C88">
-        <v>-2228.827374402007</v>
+        <v>-2270.729267600263</v>
       </c>
       <c r="D88">
-        <v>560.7546255979926</v>
+        <v>554.8897323997369</v>
       </c>
       <c r="E88">
-        <v>1578.482</v>
+        <v>1614.519</v>
       </c>
       <c r="F88">
-        <v>3099.182</v>
+        <v>3135.219</v>
       </c>
       <c r="G88">
         <v>309.6</v>
@@ -8625,37 +8625,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M88">
-        <v>730.7871156</v>
+        <v>739.2846402</v>
       </c>
       <c r="N88">
-        <v>-557.1537822666667</v>
+        <v>-565.6513068666667</v>
       </c>
       <c r="O88">
-        <v>-128.1453699213333</v>
+        <v>-130.0998005793333</v>
       </c>
       <c r="P88">
-        <v>-429.0084123453333</v>
+        <v>-435.5515062873334</v>
       </c>
       <c r="Q88">
-        <v>-340.8084123453334</v>
+        <v>-347.3515062873334</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2418342796561133</v>
+        <v>0.2569138396296605</v>
       </c>
       <c r="T88">
-        <v>3.032587959908184</v>
+        <v>3.265863956824198</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05464746957652392</v>
+        <v>0.054019337742311</v>
       </c>
       <c r="W88">
-        <v>0.2229141266738557</v>
+        <v>0.2230622401603631</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2375976938109735</v>
+        <v>0.2348666858361348</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8671,22 +8671,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2274629480913717</v>
+        <v>0.2293629480913717</v>
       </c>
       <c r="C89">
-        <v>-2270.729267600263</v>
+        <v>-2312.509749618403</v>
       </c>
       <c r="D89">
-        <v>554.8897323997369</v>
+        <v>549.1462503815974</v>
       </c>
       <c r="E89">
-        <v>1614.519</v>
+        <v>1650.556</v>
       </c>
       <c r="F89">
-        <v>3135.219</v>
+        <v>3171.256</v>
       </c>
       <c r="G89">
         <v>309.6</v>
@@ -8707,37 +8707,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M89">
-        <v>739.2846402</v>
+        <v>747.7821648</v>
       </c>
       <c r="N89">
-        <v>-565.6513068666667</v>
+        <v>-574.1488314666667</v>
       </c>
       <c r="O89">
-        <v>-130.0998005793333</v>
+        <v>-132.0542312373333</v>
       </c>
       <c r="P89">
-        <v>-435.5515062873334</v>
+        <v>-442.0946002293334</v>
       </c>
       <c r="Q89">
-        <v>-347.3515062873334</v>
+        <v>-353.8946002293334</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2569138396296605</v>
+        <v>0.2745066595987988</v>
       </c>
       <c r="T89">
-        <v>3.265863956824198</v>
+        <v>3.538019286559548</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.054019337742311</v>
+        <v>0.05340548163160291</v>
       </c>
       <c r="W89">
-        <v>0.2230622401603631</v>
+        <v>0.223206987431268</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2348666858361348</v>
+        <v>0.2321977462243605</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8753,22 +8753,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2293629480913717</v>
+        <v>0.2312629480913718</v>
       </c>
       <c r="C90">
-        <v>-2312.509749618403</v>
+        <v>-2354.172551895691</v>
       </c>
       <c r="D90">
-        <v>549.1462503815974</v>
+        <v>543.5204481043087</v>
       </c>
       <c r="E90">
-        <v>1650.556</v>
+        <v>1686.593</v>
       </c>
       <c r="F90">
-        <v>3171.256</v>
+        <v>3207.293</v>
       </c>
       <c r="G90">
         <v>309.6</v>
@@ -8789,37 +8789,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M90">
-        <v>747.7821648</v>
+        <v>756.2796893999999</v>
       </c>
       <c r="N90">
-        <v>-574.1488314666667</v>
+        <v>-582.6463560666666</v>
       </c>
       <c r="O90">
-        <v>-132.0542312373333</v>
+        <v>-134.0086618953333</v>
       </c>
       <c r="P90">
-        <v>-442.0946002293334</v>
+        <v>-448.6376941713333</v>
       </c>
       <c r="Q90">
-        <v>-353.8946002293334</v>
+        <v>-360.4376941713333</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2745066595987988</v>
+        <v>0.2952981741077806</v>
       </c>
       <c r="T90">
-        <v>3.538019286559548</v>
+        <v>3.859657403519507</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05340548163160291</v>
+        <v>0.0528054200402366</v>
       </c>
       <c r="W90">
-        <v>0.223206987431268</v>
+        <v>0.2233484819545122</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2321977462243605</v>
+        <v>0.2295887827836374</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8835,22 +8835,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2312629480913718</v>
+        <v>0.2331629480913717</v>
       </c>
       <c r="C91">
-        <v>-2354.172551895691</v>
+        <v>-2395.721254513086</v>
       </c>
       <c r="D91">
-        <v>543.5204481043087</v>
+        <v>538.0087454869133</v>
       </c>
       <c r="E91">
-        <v>1686.593</v>
+        <v>1722.63</v>
       </c>
       <c r="F91">
-        <v>3207.293</v>
+        <v>3243.33</v>
       </c>
       <c r="G91">
         <v>309.6</v>
@@ -8871,37 +8871,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M91">
-        <v>756.2796893999999</v>
+        <v>764.777214</v>
       </c>
       <c r="N91">
-        <v>-582.6463560666666</v>
+        <v>-591.1438806666666</v>
       </c>
       <c r="O91">
-        <v>-134.0086618953333</v>
+        <v>-135.9630925533333</v>
       </c>
       <c r="P91">
-        <v>-448.6376941713333</v>
+        <v>-455.1807881133333</v>
       </c>
       <c r="Q91">
-        <v>-360.4376941713333</v>
+        <v>-366.9807881133333</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2952981741077806</v>
+        <v>0.3202479915185587</v>
       </c>
       <c r="T91">
-        <v>3.859657403519507</v>
+        <v>4.245623143871459</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.0528054200402366</v>
+        <v>0.05221869315090064</v>
       </c>
       <c r="W91">
-        <v>0.2233484819545122</v>
+        <v>0.2234868321550176</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2295887827836374</v>
+        <v>0.2270377963082636</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8917,22 +8917,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2331629480913717</v>
+        <v>0.2350629480913718</v>
       </c>
       <c r="C92">
-        <v>-2395.721254513086</v>
+        <v>-2437.15929379063</v>
       </c>
       <c r="D92">
-        <v>538.0087454869133</v>
+        <v>532.6077062093698</v>
       </c>
       <c r="E92">
-        <v>1722.63</v>
+        <v>1758.667</v>
       </c>
       <c r="F92">
-        <v>3243.33</v>
+        <v>3279.367</v>
       </c>
       <c r="G92">
         <v>309.6</v>
@@ -8953,37 +8953,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M92">
-        <v>764.777214</v>
+        <v>773.2747386</v>
       </c>
       <c r="N92">
-        <v>-591.1438806666666</v>
+        <v>-599.6414052666667</v>
       </c>
       <c r="O92">
-        <v>-135.9630925533333</v>
+        <v>-137.9175232113333</v>
       </c>
       <c r="P92">
-        <v>-455.1807881133333</v>
+        <v>-461.7238820553333</v>
       </c>
       <c r="Q92">
-        <v>-366.9807881133333</v>
+        <v>-373.5238820553333</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3202479915185587</v>
+        <v>0.3507422127983986</v>
       </c>
       <c r="T92">
-        <v>4.245623143871459</v>
+        <v>4.717359048746066</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05221869315090064</v>
+        <v>0.0516448613580336</v>
       </c>
       <c r="W92">
-        <v>0.2234868321550176</v>
+        <v>0.2236221416917757</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2270377963082636</v>
+        <v>0.2245428754697113</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8999,22 +8999,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2350629480913718</v>
+        <v>0.2369629480913718</v>
       </c>
       <c r="C93">
-        <v>-2437.15929379063</v>
+        <v>-2478.48996943176</v>
       </c>
       <c r="D93">
-        <v>532.6077062093698</v>
+        <v>527.3140305682404</v>
       </c>
       <c r="E93">
-        <v>1758.667</v>
+        <v>1794.704</v>
       </c>
       <c r="F93">
-        <v>3279.367</v>
+        <v>3315.404</v>
       </c>
       <c r="G93">
         <v>309.6</v>
@@ -9035,37 +9035,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M93">
-        <v>773.2747386</v>
+        <v>781.7722632</v>
       </c>
       <c r="N93">
-        <v>-599.6414052666667</v>
+        <v>-608.1389298666667</v>
       </c>
       <c r="O93">
-        <v>-137.9175232113333</v>
+        <v>-139.8719538693333</v>
       </c>
       <c r="P93">
-        <v>-461.7238820553333</v>
+        <v>-468.2669759973334</v>
       </c>
       <c r="Q93">
-        <v>-373.5238820553333</v>
+        <v>-380.0669759973334</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3507422127983986</v>
+        <v>0.3888599893981985</v>
       </c>
       <c r="T93">
-        <v>4.717359048746066</v>
+        <v>5.307028929839325</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0516448613580336</v>
+        <v>0.05108350416935931</v>
       </c>
       <c r="W93">
-        <v>0.2236221416917757</v>
+        <v>0.2237545097168651</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2245428754697113</v>
+        <v>0.2221021920406927</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9081,22 +9081,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2369629480913718</v>
+        <v>0.2388629480913718</v>
       </c>
       <c r="C94">
-        <v>-2478.48996943176</v>
+        <v>-2519.716451245771</v>
       </c>
       <c r="D94">
-        <v>527.3140305682404</v>
+        <v>522.1245487542284</v>
       </c>
       <c r="E94">
-        <v>1794.704</v>
+        <v>1830.741</v>
       </c>
       <c r="F94">
-        <v>3315.404</v>
+        <v>3351.441</v>
       </c>
       <c r="G94">
         <v>309.6</v>
@@ -9117,37 +9117,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M94">
-        <v>781.7722632</v>
+        <v>790.2697878</v>
       </c>
       <c r="N94">
-        <v>-608.1389298666667</v>
+        <v>-616.6364544666667</v>
       </c>
       <c r="O94">
-        <v>-139.8719538693333</v>
+        <v>-141.8263845273333</v>
       </c>
       <c r="P94">
-        <v>-468.2669759973334</v>
+        <v>-474.8100699393333</v>
       </c>
       <c r="Q94">
-        <v>-380.0669759973334</v>
+        <v>-386.6100699393334</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3888599893981985</v>
+        <v>0.4378685593122268</v>
       </c>
       <c r="T94">
-        <v>5.307028929839325</v>
+        <v>6.065175919816372</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05108350416935931</v>
+        <v>0.05053421917829094</v>
       </c>
       <c r="W94">
-        <v>0.2237545097168651</v>
+        <v>0.223884031117759</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2221021920406927</v>
+        <v>0.2197139964273519</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9163,22 +9163,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2388629480913718</v>
+        <v>0.2407629480913717</v>
       </c>
       <c r="C95">
-        <v>-2519.716451245771</v>
+        <v>-2560.841785477197</v>
       </c>
       <c r="D95">
-        <v>522.1245487542284</v>
+        <v>517.0362145228029</v>
       </c>
       <c r="E95">
-        <v>1830.741</v>
+        <v>1866.778</v>
       </c>
       <c r="F95">
-        <v>3351.441</v>
+        <v>3387.478</v>
       </c>
       <c r="G95">
         <v>309.6</v>
@@ -9199,37 +9199,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M95">
-        <v>790.2697878</v>
+        <v>798.7673124</v>
       </c>
       <c r="N95">
-        <v>-616.6364544666667</v>
+        <v>-625.1339790666667</v>
       </c>
       <c r="O95">
-        <v>-141.8263845273333</v>
+        <v>-143.7808151853334</v>
       </c>
       <c r="P95">
-        <v>-474.8100699393333</v>
+        <v>-481.3531638813333</v>
       </c>
       <c r="Q95">
-        <v>-386.6100699393334</v>
+        <v>-393.1531638813333</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4378685593122268</v>
+        <v>0.503213319197598</v>
       </c>
       <c r="T95">
-        <v>6.065175919816372</v>
+        <v>7.076038573119103</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05053421917829094</v>
+        <v>0.04999662110192614</v>
       </c>
       <c r="W95">
-        <v>0.223884031117759</v>
+        <v>0.2240107967441658</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2197139964273519</v>
+        <v>0.2173766134866354</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9245,22 +9245,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2407629480913717</v>
+        <v>0.2426629480913718</v>
       </c>
       <c r="C96">
-        <v>-2560.841785477197</v>
+        <v>-2601.86890076866</v>
       </c>
       <c r="D96">
-        <v>517.0362145228029</v>
+        <v>512.0460992313394</v>
       </c>
       <c r="E96">
-        <v>1866.778</v>
+        <v>1902.815</v>
       </c>
       <c r="F96">
-        <v>3387.478</v>
+        <v>3423.515</v>
       </c>
       <c r="G96">
         <v>309.6</v>
@@ -9281,37 +9281,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M96">
-        <v>798.7673124</v>
+        <v>807.2648370000001</v>
       </c>
       <c r="N96">
-        <v>-625.1339790666667</v>
+        <v>-633.6315036666667</v>
       </c>
       <c r="O96">
-        <v>-143.7808151853334</v>
+        <v>-145.7352458433334</v>
       </c>
       <c r="P96">
-        <v>-481.3531638813333</v>
+        <v>-487.8962578233334</v>
       </c>
       <c r="Q96">
-        <v>-393.1531638813333</v>
+        <v>-399.6962578233334</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.503213319197598</v>
+        <v>0.594695983037118</v>
       </c>
       <c r="T96">
-        <v>7.076038573119103</v>
+        <v>8.491246287742928</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04999662110192614</v>
+        <v>0.0494703408798006</v>
       </c>
       <c r="W96">
-        <v>0.2240107967441658</v>
+        <v>0.224134893620543</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2173766134866354</v>
+        <v>0.2150884386078287</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9327,22 +9327,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2426629480913718</v>
+        <v>0.2445629480913717</v>
       </c>
       <c r="C97">
-        <v>-2601.86890076866</v>
+        <v>-2642.800613781734</v>
       </c>
       <c r="D97">
-        <v>512.0460992313394</v>
+        <v>507.1513862182666</v>
       </c>
       <c r="E97">
-        <v>1902.815</v>
+        <v>1938.852</v>
       </c>
       <c r="F97">
-        <v>3423.515</v>
+        <v>3459.552</v>
       </c>
       <c r="G97">
         <v>309.6</v>
@@ -9363,37 +9363,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M97">
-        <v>807.2648370000001</v>
+        <v>815.7623616000001</v>
       </c>
       <c r="N97">
-        <v>-633.6315036666667</v>
+        <v>-642.1290282666668</v>
       </c>
       <c r="O97">
-        <v>-145.7352458433334</v>
+        <v>-147.6896765013334</v>
       </c>
       <c r="P97">
-        <v>-487.8962578233334</v>
+        <v>-494.4393517653334</v>
       </c>
       <c r="Q97">
-        <v>-399.6962578233334</v>
+        <v>-406.2393517653334</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.594695983037118</v>
+        <v>0.7319199787963978</v>
       </c>
       <c r="T97">
-        <v>8.491246287742928</v>
+        <v>10.61405785967866</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0494703408798006</v>
+        <v>0.04895502482896934</v>
       </c>
       <c r="W97">
-        <v>0.224134893620543</v>
+        <v>0.224256405145329</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2150884386078287</v>
+        <v>0.2128479340389972</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9409,22 +9409,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2445629480913717</v>
+        <v>0.2464629480913717</v>
       </c>
       <c r="C98">
-        <v>-2642.800613781733</v>
+        <v>-2683.639634498462</v>
       </c>
       <c r="D98">
-        <v>507.1513862182666</v>
+        <v>502.3493655015376</v>
       </c>
       <c r="E98">
-        <v>1938.852</v>
+        <v>1974.889</v>
       </c>
       <c r="F98">
-        <v>3459.552</v>
+        <v>3495.589</v>
       </c>
       <c r="G98">
         <v>309.6</v>
@@ -9445,37 +9445,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M98">
-        <v>815.7623616</v>
+        <v>824.2598862</v>
       </c>
       <c r="N98">
-        <v>-642.1290282666666</v>
+        <v>-650.6265528666667</v>
       </c>
       <c r="O98">
-        <v>-147.6896765013333</v>
+        <v>-149.6441071593333</v>
       </c>
       <c r="P98">
-        <v>-494.4393517653333</v>
+        <v>-500.9824457073333</v>
       </c>
       <c r="Q98">
-        <v>-406.2393517653333</v>
+        <v>-412.7824457073334</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7319199787963959</v>
+        <v>0.9606266383951947</v>
       </c>
       <c r="T98">
-        <v>10.61405785967864</v>
+        <v>14.15207714623818</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04895502482896934</v>
+        <v>0.04845033385135111</v>
       </c>
       <c r="W98">
-        <v>0.224256405145329</v>
+        <v>0.2243754112778514</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2128479340389972</v>
+        <v>0.2106536254406569</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9491,22 +9491,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2464629480913717</v>
+        <v>0.2483629480913717</v>
       </c>
       <c r="C99">
-        <v>-2683.639634498462</v>
+        <v>-2724.388571224533</v>
       </c>
       <c r="D99">
-        <v>502.3493655015376</v>
+        <v>497.6374287754666</v>
       </c>
       <c r="E99">
-        <v>1974.889</v>
+        <v>2010.926</v>
       </c>
       <c r="F99">
-        <v>3495.589</v>
+        <v>3531.626</v>
       </c>
       <c r="G99">
         <v>309.6</v>
@@ -9527,37 +9527,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M99">
-        <v>824.2598862</v>
+        <v>832.7574108</v>
       </c>
       <c r="N99">
-        <v>-650.6265528666667</v>
+        <v>-659.1240774666667</v>
       </c>
       <c r="O99">
-        <v>-149.6441071593333</v>
+        <v>-151.5985378173334</v>
       </c>
       <c r="P99">
-        <v>-500.9824457073333</v>
+        <v>-507.5255396493333</v>
       </c>
       <c r="Q99">
-        <v>-412.7824457073334</v>
+        <v>-419.3255396493333</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9606266383951947</v>
+        <v>1.418039957592792</v>
       </c>
       <c r="T99">
-        <v>14.15207714623818</v>
+        <v>21.22811571935727</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04845033385135111</v>
+        <v>0.04795594268960262</v>
       </c>
       <c r="W99">
-        <v>0.2243754112778514</v>
+        <v>0.2244919887137917</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2106536254406569</v>
+        <v>0.2085040986504462</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9573,22 +9573,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2483629480913717</v>
+        <v>0.2502629480913717</v>
       </c>
       <c r="C100">
-        <v>-2724.388571224533</v>
+        <v>-2765.049935313477</v>
       </c>
       <c r="D100">
-        <v>497.6374287754666</v>
+        <v>493.0130646865226</v>
       </c>
       <c r="E100">
-        <v>2010.926</v>
+        <v>2046.963</v>
       </c>
       <c r="F100">
-        <v>3531.626</v>
+        <v>3567.663</v>
       </c>
       <c r="G100">
         <v>309.6</v>
@@ -9609,37 +9609,37 @@
         <v>173.6333333333333</v>
       </c>
       <c r="M100">
-        <v>832.7574108</v>
+        <v>841.2549354</v>
       </c>
       <c r="N100">
-        <v>-659.1240774666667</v>
+        <v>-667.6216020666667</v>
       </c>
       <c r="O100">
-        <v>-151.5985378173334</v>
+        <v>-153.5529684753334</v>
       </c>
       <c r="P100">
-        <v>-507.5255396493333</v>
+        <v>-514.0686335913333</v>
       </c>
       <c r="Q100">
-        <v>-419.3255396493333</v>
+        <v>-425.8686335913333</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.418039957592792</v>
+        <v>2.790279915185584</v>
       </c>
       <c r="T100">
-        <v>21.22811571935727</v>
+        <v>42.45623143871455</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04795594268960262</v>
+        <v>0.04747153922809148</v>
       </c>
       <c r="W100">
-        <v>0.2244919887137917</v>
+        <v>0.224606211050016</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9647,91 +9647,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2085040986504462</v>
+        <v>0.206397996643876</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2502629480913717</v>
-      </c>
-      <c r="C101">
-        <v>-2765.049935313477</v>
-      </c>
-      <c r="D101">
-        <v>493.0130646865226</v>
-      </c>
-      <c r="E101">
-        <v>2046.963</v>
-      </c>
-      <c r="F101">
-        <v>3567.663</v>
-      </c>
-      <c r="G101">
-        <v>309.6</v>
-      </c>
-      <c r="H101">
-        <v>2083</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>261.8333333333333</v>
-      </c>
-      <c r="K101">
-        <v>88.2</v>
-      </c>
-      <c r="L101">
-        <v>173.6333333333333</v>
-      </c>
-      <c r="M101">
-        <v>841.2549354</v>
-      </c>
-      <c r="N101">
-        <v>-667.6216020666667</v>
-      </c>
-      <c r="O101">
-        <v>-153.5529684753334</v>
-      </c>
-      <c r="P101">
-        <v>-514.0686335913333</v>
-      </c>
-      <c r="Q101">
-        <v>-425.8686335913333</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.790279915185584</v>
-      </c>
-      <c r="T101">
-        <v>42.45623143871455</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04747153922809148</v>
-      </c>
-      <c r="W101">
-        <v>0.224606211050016</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.206397996643876</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
